--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
         <v>45039</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2637,7 +2637,7 @@
         <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>45002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2983,7 +2983,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>45518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3773,7 +3773,7 @@
         <v>44956</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3991,7 +3991,7 @@
         <v>46119</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>44814</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45839</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45600</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44472</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45212</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>45518</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>46044</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46112</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>44986</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>46079</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45789</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>45946</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5876,7 +5876,7 @@
         <v>45965</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5983,7 +5983,7 @@
         <v>44578</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>45272</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6420,7 +6420,7 @@
         <v>46071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6531,7 +6531,7 @@
         <v>46119</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6638,7 +6638,7 @@
         <v>45666</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6750,7 +6750,7 @@
         <v>44790</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6866,7 +6866,7 @@
         <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6973,7 +6973,7 @@
         <v>45142</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>45883</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7196,7 +7196,7 @@
         <v>45883</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44830</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>45530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44637</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44826</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8066,7 +8066,7 @@
         <v>45219</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8176,7 +8176,7 @@
         <v>44865</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8291,7 +8291,7 @@
         <v>45400</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8397,7 +8397,7 @@
         <v>44798</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8503,7 +8503,7 @@
         <v>44474</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8609,7 +8609,7 @@
         <v>44971</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8715,7 +8715,7 @@
         <v>45838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
         <v>46155</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8927,7 +8927,7 @@
         <v>45211</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>45068</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46106</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>46044</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>44907</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46068</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>45166</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44848</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9896,7 +9896,7 @@
         <v>44785</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10002,7 +10002,7 @@
         <v>46258</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44624</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44986</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>45798</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44697</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44746</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44503</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45140</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45510</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>44463</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11500,7 +11500,7 @@
         <v>45007</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11610,7 +11610,7 @@
         <v>45540</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>44774</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11820,7 +11820,7 @@
         <v>45348</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11925,7 +11925,7 @@
         <v>45740</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12140,7 +12140,7 @@
         <v>45343</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12245,7 +12245,7 @@
         <v>45182</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12350,7 +12350,7 @@
         <v>45931</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45141</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12565,7 +12565,7 @@
         <v>44518</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12670,7 +12670,7 @@
         <v>44572</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12780,7 +12780,7 @@
         <v>46149</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>45740</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12995,7 +12995,7 @@
         <v>45156</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13105,7 +13105,7 @@
         <v>45954</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>45643</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13320,7 +13320,7 @@
         <v>45222</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13425,7 +13425,7 @@
         <v>44463</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13530,7 +13530,7 @@
         <v>45586</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44624</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13740,7 +13740,7 @@
         <v>46168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13850,7 +13850,7 @@
         <v>45163</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>44637</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14065,7 +14065,7 @@
         <v>46035</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14175,7 +14175,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14289,7 +14289,7 @@
         <v>44911</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14399,7 +14399,7 @@
         <v>44953</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14504,7 +14504,7 @@
         <v>46181</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>46056</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45105</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>46181</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15047,7 +15047,7 @@
         <v>46071</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15157,7 +15157,7 @@
         <v>46079</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15267,7 +15267,7 @@
         <v>44495</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15377,7 +15377,7 @@
         <v>44865</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15487,7 +15487,7 @@
         <v>45350</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15592,7 +15592,7 @@
         <v>45377</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15697,7 +15697,7 @@
         <v>44854</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44503</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45740</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>46209</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16127,7 +16127,7 @@
         <v>45211</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>45191</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16337,7 +16337,7 @@
         <v>45196</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16447,7 +16447,7 @@
         <v>45624</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16552,7 +16552,7 @@
         <v>44501</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16625,7 +16625,7 @@
         <v>44724</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>44536</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16771,7 +16771,7 @@
         <v>44458</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16844,7 +16844,7 @@
         <v>44614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16917,7 +16917,7 @@
         <v>44535</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16990,7 +16990,7 @@
         <v>44722</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17068,7 +17068,7 @@
         <v>44869</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17146,7 +17146,7 @@
         <v>44473</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17219,7 +17219,7 @@
         <v>44608</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17297,7 +17297,7 @@
         <v>44752</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17370,7 +17370,7 @@
         <v>44720</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17448,7 +17448,7 @@
         <v>44873</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17521,7 +17521,7 @@
         <v>44769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17594,7 +17594,7 @@
         <v>44745</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17667,7 +17667,7 @@
         <v>44461</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44839</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44579</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44807</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>44855</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -18037,7 +18037,7 @@
         <v>44879</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18110,7 +18110,7 @@
         <v>44463</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18183,7 +18183,7 @@
         <v>44739</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18256,7 +18256,7 @@
         <v>44769</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>44640</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44770</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18480,7 +18480,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>44725</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18626,7 +18626,7 @@
         <v>44643</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18699,7 +18699,7 @@
         <v>44474</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44778</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44588</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18923,7 +18923,7 @@
         <v>44769</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18996,7 +18996,7 @@
         <v>44839</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19069,7 +19069,7 @@
         <v>44886</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>44854</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19215,7 +19215,7 @@
         <v>44697</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19288,7 +19288,7 @@
         <v>44769</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19361,7 +19361,7 @@
         <v>44578</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19439,7 +19439,7 @@
         <v>44846</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19517,7 +19517,7 @@
         <v>44636</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19590,7 +19590,7 @@
         <v>44752</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19663,7 +19663,7 @@
         <v>44752</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19736,7 +19736,7 @@
         <v>44566</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19814,7 +19814,7 @@
         <v>44862</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19887,7 +19887,7 @@
         <v>44610</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>44643</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>44636</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>44818</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>44705</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44980</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>44868</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45531</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20481,7 +20481,7 @@
         <v>45555</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20554,7 +20554,7 @@
         <v>45378</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44517</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44531</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>44785</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>44914</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>44986</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>44495</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>44544</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45510</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>44473</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>45636</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45068</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>44796</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45225</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45597</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>45239</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45226</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45270</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>44970</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21961,7 +21961,7 @@
         <v>45166</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -22034,7 +22034,7 @@
         <v>45149</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22112,7 +22112,7 @@
         <v>45309</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22185,7 +22185,7 @@
         <v>44733</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22258,7 +22258,7 @@
         <v>45482</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22331,7 +22331,7 @@
         <v>45209</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22404,7 +22404,7 @@
         <v>44522</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44979</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>44931</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22633,7 +22633,7 @@
         <v>45147</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22706,7 +22706,7 @@
         <v>44859</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45244</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44624</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22930,7 +22930,7 @@
         <v>45163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -23003,7 +23003,7 @@
         <v>45740</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -23081,7 +23081,7 @@
         <v>45311</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>44588</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23227,7 +23227,7 @@
         <v>45299</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23300,7 +23300,7 @@
         <v>44872</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>44896</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23451,7 +23451,7 @@
         <v>44859</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45057</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45228</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45034</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>44602</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45398</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45089</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>45667</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -24040,7 +24040,7 @@
         <v>44761</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24113,7 +24113,7 @@
         <v>45260</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>44838</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>45566</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24332,7 +24332,7 @@
         <v>45581</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24405,7 +24405,7 @@
         <v>45358</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24478,7 +24478,7 @@
         <v>44722</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24551,7 +24551,7 @@
         <v>44722</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>44785</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>44616</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44466</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>45553</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45103</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>45213</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25140,7 +25140,7 @@
         <v>45104</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25213,7 +25213,7 @@
         <v>45322</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25286,7 +25286,7 @@
         <v>45280</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25359,7 +25359,7 @@
         <v>44862</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>44524</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25510,7 +25510,7 @@
         <v>45895</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45869</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44807</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25729,7 +25729,7 @@
         <v>44522</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45411</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>44979</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>45555</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -26021,7 +26021,7 @@
         <v>45791</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>45081</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45081</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>44988</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26391,7 +26391,7 @@
         <v>45228</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45022</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26537,7 +26537,7 @@
         <v>45924</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>45632</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45022</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45926</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26839,7 +26839,7 @@
         <v>44897</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>44778</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26990,7 +26990,7 @@
         <v>44463</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>45331</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45933</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27214,7 +27214,7 @@
         <v>45932</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>45066</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44979</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27438,7 +27438,7 @@
         <v>45330</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27516,7 +27516,7 @@
         <v>44864</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>44855</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27662,7 +27662,7 @@
         <v>45250</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27740,7 +27740,7 @@
         <v>45250</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27813,7 +27813,7 @@
         <v>44855</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27886,7 +27886,7 @@
         <v>45888</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45946</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -28032,7 +28032,7 @@
         <v>45528</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28105,7 +28105,7 @@
         <v>45306</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28178,7 +28178,7 @@
         <v>44896</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44970</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28329,7 +28329,7 @@
         <v>45952</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28402,7 +28402,7 @@
         <v>45140</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28475,7 +28475,7 @@
         <v>45964</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28548,7 +28548,7 @@
         <v>45964</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28621,7 +28621,7 @@
         <v>45713</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>44957</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28767,7 +28767,7 @@
         <v>45209</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28840,7 +28840,7 @@
         <v>45244</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>44991</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28991,7 +28991,7 @@
         <v>45974</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29064,7 +29064,7 @@
         <v>45048</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29137,7 +29137,7 @@
         <v>45056</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29210,7 +29210,7 @@
         <v>45574</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29288,7 +29288,7 @@
         <v>45230</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45119</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29434,7 +29434,7 @@
         <v>44566</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29507,7 +29507,7 @@
         <v>44624</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>45224</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29658,7 +29658,7 @@
         <v>45993</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29731,7 +29731,7 @@
         <v>45993</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29804,7 +29804,7 @@
         <v>45993</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29877,7 +29877,7 @@
         <v>45041</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29950,7 +29950,7 @@
         <v>45222</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -30023,7 +30023,7 @@
         <v>45166</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30096,7 +30096,7 @@
         <v>44701</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45740</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30247,7 +30247,7 @@
         <v>44909</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30325,7 +30325,7 @@
         <v>45518</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30398,7 +30398,7 @@
         <v>45271</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45994</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30549,7 +30549,7 @@
         <v>45995</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30622,7 +30622,7 @@
         <v>46069</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45995</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30773,7 +30773,7 @@
         <v>45994</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45257</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30924,7 +30924,7 @@
         <v>45632</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>45315</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45321</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>46000</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>44676</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>45013</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>45230</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45230</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>46168</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31591,7 +31591,7 @@
         <v>46168</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>44459</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31742,7 +31742,7 @@
         <v>46168</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31815,7 +31815,7 @@
         <v>46168</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31893,7 +31893,7 @@
         <v>46168</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31966,7 +31966,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32044,7 +32044,7 @@
         <v>46121</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32117,7 +32117,7 @@
         <v>46170</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45163</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>46170</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32361,7 +32361,7 @@
         <v>44741</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>44636</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32507,7 +32507,7 @@
         <v>45618</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32580,7 +32580,7 @@
         <v>46036</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32658,7 +32658,7 @@
         <v>44887</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32731,7 +32731,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>44911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32882,7 +32882,7 @@
         <v>45932</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>46044</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -33028,7 +33028,7 @@
         <v>46175</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45114</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33174,7 +33174,7 @@
         <v>46175</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33247,7 +33247,7 @@
         <v>46176</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33325,7 +33325,7 @@
         <v>46181</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33398,7 +33398,7 @@
         <v>46181</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33471,7 +33471,7 @@
         <v>45161</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33544,7 +33544,7 @@
         <v>45012</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33622,7 +33622,7 @@
         <v>46056</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33695,7 +33695,7 @@
         <v>44887</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33768,7 +33768,7 @@
         <v>46044</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44958</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33919,7 +33919,7 @@
         <v>44907</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33992,7 +33992,7 @@
         <v>44900</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34065,7 +34065,7 @@
         <v>45072</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>46181</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34216,7 +34216,7 @@
         <v>45217</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34294,7 +34294,7 @@
         <v>45114</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34367,7 +34367,7 @@
         <v>46071</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34440,7 +34440,7 @@
         <v>45299</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>46071</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34586,7 +34586,7 @@
         <v>46170</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34664,7 +34664,7 @@
         <v>45189</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34742,7 +34742,7 @@
         <v>45082</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34815,7 +34815,7 @@
         <v>46077</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34888,7 +34888,7 @@
         <v>46080</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34966,7 +34966,7 @@
         <v>46080</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -35044,7 +35044,7 @@
         <v>45030</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35117,7 +35117,7 @@
         <v>46079</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>46079</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>46185</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35346,7 +35346,7 @@
         <v>46079</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35424,7 +35424,7 @@
         <v>46080</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>46082</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35575,7 +35575,7 @@
         <v>46083</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>46183</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>46185</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35804,7 +35804,7 @@
         <v>44887</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35877,7 +35877,7 @@
         <v>46188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35950,7 +35950,7 @@
         <v>45169</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -36023,7 +36023,7 @@
         <v>45225</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>45501</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45555</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>46188</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44846</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>46188</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36466,7 +36466,7 @@
         <v>45161</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36539,7 +36539,7 @@
         <v>46091</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36612,7 +36612,7 @@
         <v>45250</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36690,7 +36690,7 @@
         <v>45211</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36763,7 +36763,7 @@
         <v>46196</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36836,7 +36836,7 @@
         <v>45225</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36909,7 +36909,7 @@
         <v>44848</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36987,7 +36987,7 @@
         <v>45441</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37060,7 +37060,7 @@
         <v>46108</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>44614</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45720</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37284,7 +37284,7 @@
         <v>46112</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>46113</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37430,7 +37430,7 @@
         <v>45230</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37503,7 +37503,7 @@
         <v>45540</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37576,7 +37576,7 @@
         <v>44614</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>46244</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37722,7 +37722,7 @@
         <v>46126</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>46126</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37868,7 +37868,7 @@
         <v>46125</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37946,7 +37946,7 @@
         <v>46126</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -38019,7 +38019,7 @@
         <v>46121</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38092,7 +38092,7 @@
         <v>46121</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38165,7 +38165,7 @@
         <v>44909</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38243,7 +38243,7 @@
         <v>46129</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38316,7 +38316,7 @@
         <v>45327</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38389,7 +38389,7 @@
         <v>45001</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38467,7 +38467,7 @@
         <v>46121</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38540,7 +38540,7 @@
         <v>46132</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>46132</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44553</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38769,7 +38769,7 @@
         <v>46134</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38842,7 +38842,7 @@
         <v>45345</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45888</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45805</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45718</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39134,7 +39134,7 @@
         <v>44648</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39207,7 +39207,7 @@
         <v>44739</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39280,7 +39280,7 @@
         <v>45454</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39353,7 +39353,7 @@
         <v>45478</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39426,7 +39426,7 @@
         <v>46251</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39504,7 +39504,7 @@
         <v>45713</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39577,7 +39577,7 @@
         <v>44580</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45140</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39728,7 +39728,7 @@
         <v>46251</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39806,7 +39806,7 @@
         <v>46251</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39884,7 +39884,7 @@
         <v>44819</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39957,7 +39957,7 @@
         <v>46205</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -40030,7 +40030,7 @@
         <v>46250</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40103,7 +40103,7 @@
         <v>44769</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>45110</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45250</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>45161</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40395,7 +40395,7 @@
         <v>44960</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40468,7 +40468,7 @@
         <v>46198</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45244</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40619,7 +40619,7 @@
         <v>45328</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40692,7 +40692,7 @@
         <v>46253</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40765,7 +40765,7 @@
         <v>45175</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40838,7 +40838,7 @@
         <v>45036</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40911,7 +40911,7 @@
         <v>44907</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40984,7 +40984,7 @@
         <v>45365</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41057,7 +41057,7 @@
         <v>45244</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41130,7 +41130,7 @@
         <v>46258</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41208,7 +41208,7 @@
         <v>46258</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41286,7 +41286,7 @@
         <v>44634</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41359,7 +41359,7 @@
         <v>46258</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41437,7 +41437,7 @@
         <v>45176</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41510,7 +41510,7 @@
         <v>46252</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41583,7 +41583,7 @@
         <v>45216</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41661,7 +41661,7 @@
         <v>46252</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41734,7 +41734,7 @@
         <v>46252</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41807,7 +41807,7 @@
         <v>45180</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41880,7 +41880,7 @@
         <v>45256</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41953,7 +41953,7 @@
         <v>45007</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -42026,7 +42026,7 @@
         <v>45448</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>46265</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42172,7 +42172,7 @@
         <v>46266</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45386</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42323,7 +42323,7 @@
         <v>46267</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42401,7 +42401,7 @@
         <v>46267</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42479,7 +42479,7 @@
         <v>44610</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>46267</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42630,7 +42630,7 @@
         <v>45014</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>45671</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45163</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42854,7 +42854,7 @@
         <v>44958</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>45777</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>46273</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43088,7 +43088,7 @@
         <v>46273</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43166,7 +43166,7 @@
         <v>46229</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>46273</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>45414</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>45350</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>44883</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>44852</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45008</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45790</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45790</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45790</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43974,7 +43974,7 @@
         <v>46249</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -44047,7 +44047,7 @@
         <v>45610</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44120,7 +44120,7 @@
         <v>45555</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>45797</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44266,7 +44266,7 @@
         <v>46240</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>45798</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44412,7 +44412,7 @@
         <v>45798</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44485,7 +44485,7 @@
         <v>45702</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44558,7 +44558,7 @@
         <v>45798</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44631,7 +44631,7 @@
         <v>45798</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44709,7 +44709,7 @@
         <v>46283</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44782,7 +44782,7 @@
         <v>45684</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44855,7 +44855,7 @@
         <v>45817</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45830</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -45006,7 +45006,7 @@
         <v>45830</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45079,7 +45079,7 @@
         <v>45702</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45152,7 +45152,7 @@
         <v>45729</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45225,7 +45225,7 @@
         <v>44899</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>45880</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45371,7 +45371,7 @@
         <v>45883</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -45444,7 +45444,7 @@
         <v>44964</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -45522,7 +45522,7 @@
         <v>45686</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -45595,7 +45595,7 @@
         <v>44742</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>44588</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -45741,7 +45741,7 @@
         <v>44685</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -45819,7 +45819,7 @@
         <v>45446</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -45892,7 +45892,7 @@
         <v>45403</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -45965,7 +45965,7 @@
         <v>46164</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45323</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44624</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45039</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46079</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45002</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44956</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46097</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45209</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44472</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45946</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45789</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44771</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45142</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44830</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>45530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44637</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45400</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>46044</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>46068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44798</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44474</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44971</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46106</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>45166</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44624</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44596</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>46155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44785</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44986</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44697</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44746</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44503</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44881</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45377</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46056</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45740</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>46071</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>46079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45931</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45954</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45510</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>44865</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>46149</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45740</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46168</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44495</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45007</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>46181</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44572</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44637</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45740</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45163</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44774</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45343</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45222</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45586</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44518</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45141</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>45182</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45156</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45624</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44501</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44724</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44536</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44535</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44722</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44869</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44473</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>44608</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>44752</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44873</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>44769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44745</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44579</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44807</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44879</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44739</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44769</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44640</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44725</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>44474</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44778</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>44588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44769</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44839</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>44886</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44854</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44697</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>44769</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44752</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44752</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>44566</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44862</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>44610</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44643</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44636</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45720</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45311</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>44741</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45358</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45228</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44862</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45222</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45330</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45398</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45250</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45441</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44796</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45257</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45114</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44887</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45119</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45322</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45555</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45256</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45610</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45798</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45797</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45798</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45798</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45478</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45702</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45176</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>44522</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>46044</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45161</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44859</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45280</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46056</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>46044</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44616</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45014</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46071</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44838</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44958</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46077</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45226</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46079</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>46079</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>46079</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46082</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46080</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46080</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46080</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>46083</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44524</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45209</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44986</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44778</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45946</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45448</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45888</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45553</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>46108</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45684</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46113</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44911</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45581</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45636</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46125</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>46126</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44970</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44722</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46126</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46126</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46129</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>46121</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>46121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>46134</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45805</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45597</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45632</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45993</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45994</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45993</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45993</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45995</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45995</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44807</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45225</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46000</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45225</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45713</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45869</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45888</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45228</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45718</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44522</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45048</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45671</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45007</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45345</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45082</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44909</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45041</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45791</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>44979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45068</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44848</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45225</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45830</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44864</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45216</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>44466</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45224</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45260</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45271</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45103</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45022</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45104</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46069</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45081</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45081</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45001</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45702</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45729</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45147</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46168</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>46168</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44553</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44909</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45618</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>46170</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45250</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45161</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44899</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45932</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>46175</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>46175</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45163</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>44473</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44991</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44957</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>44614</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45180</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45528</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>46181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>46181</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>46181</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46183</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>44544</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45175</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46170</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>44495</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46185</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46185</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45327</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>46188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45161</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>46196</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44610</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45880</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44602</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45114</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45328</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45555</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45166</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46251</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>46250</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>46251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>46251</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44531</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>46253</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44634</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>46258</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>46258</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44676</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45454</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45740</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44785</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45230</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44846</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>46252</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>46252</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45169</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>44733</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>44907</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45315</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>46266</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>46265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44887</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45378</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46267</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45163</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>46267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>46267</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45250</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46229</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45321</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44900</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46273</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45309</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>44868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>44624</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44624</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45411</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>44970</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>44896</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>46240</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45531</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44859</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45501</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46244</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>46091</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46283</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44566</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>46249</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44960</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46286</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>44855</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44855</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45140</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45072</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45482</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45213</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45510</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44914</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>44785</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>44648</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44979</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45056</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44739</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>44769</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44872</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45239</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>44701</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45270</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45518</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45574</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45365</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45299</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45299</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45022</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45110</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45149</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45555</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45331</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>44931</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>44580</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45217</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45066</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>44907</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45667</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45230</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45230</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45013</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45566</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45386</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45777</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45350</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45252</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45008</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>44852</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>44883</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45414</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45790</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45790</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45790</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>44588</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>44685</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44964</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45686</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>44742</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45446</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45403</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46164</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1473,7 +1473,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1713,7 +1713,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1828,7 +1828,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1943,7 +1943,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2175,7 +2175,7 @@
         <v>45323</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2295,7 +2295,7 @@
         <v>44624</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>45039</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2522,7 +2522,7 @@
         <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>44495</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2753,7 +2753,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2978,7 +2978,7 @@
         <v>46079</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3093,7 +3093,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3212,7 +3212,7 @@
         <v>45002</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3437,7 +3437,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3550,7 +3550,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3659,7 +3659,7 @@
         <v>45518</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3999,7 +3999,7 @@
         <v>44956</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>46097</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>45209</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4444,7 +4444,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4558,7 +4558,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>44472</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4995,7 +4995,7 @@
         <v>45518</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5103,7 +5103,7 @@
         <v>46079</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>45212</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5550,7 +5550,7 @@
         <v>45883</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45883</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5871,7 +5871,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6089,7 +6089,7 @@
         <v>45946</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6201,7 +6201,7 @@
         <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6308,7 +6308,7 @@
         <v>46119</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6527,7 +6527,7 @@
         <v>45789</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6634,7 +6634,7 @@
         <v>45965</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>44578</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6857,7 +6857,7 @@
         <v>46205</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6964,7 +6964,7 @@
         <v>44771</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44790</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7187,7 +7187,7 @@
         <v>45142</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7303,7 +7303,7 @@
         <v>45275</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7419,7 +7419,7 @@
         <v>44830</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7526,7 +7526,7 @@
         <v>45530</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>44637</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7743,7 +7743,7 @@
         <v>44624</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7849,7 +7849,7 @@
         <v>44715</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7960,7 +7960,7 @@
         <v>44865</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8075,7 +8075,7 @@
         <v>45400</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8181,7 +8181,7 @@
         <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8292,7 +8292,7 @@
         <v>46044</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8403,7 +8403,7 @@
         <v>45211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8509,7 +8509,7 @@
         <v>46068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8615,7 +8615,7 @@
         <v>44826</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8721,7 +8721,7 @@
         <v>45838</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8827,7 +8827,7 @@
         <v>44798</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45219</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
         <v>44474</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9149,7 +9149,7 @@
         <v>44848</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9260,7 +9260,7 @@
         <v>44971</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9472,7 +9472,7 @@
         <v>46106</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>45166</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>46258</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9800,7 +9800,7 @@
         <v>44907</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9906,7 +9906,7 @@
         <v>44624</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10012,7 +10012,7 @@
         <v>44596</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10118,7 +10118,7 @@
         <v>46155</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10224,7 +10224,7 @@
         <v>44785</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10330,7 +10330,7 @@
         <v>44986</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>44697</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44746</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44503</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10756,7 +10756,7 @@
         <v>44608</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44838</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44735</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>44881</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>45377</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>46035</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44624</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>46056</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11825,7 +11825,7 @@
         <v>45740</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>46071</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>46079</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>45931</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12265,7 +12265,7 @@
         <v>45954</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45510</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12480,7 +12480,7 @@
         <v>44503</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>44865</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>46149</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45740</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12910,7 +12910,7 @@
         <v>46168</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>44495</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13130,7 +13130,7 @@
         <v>45348</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13235,7 +13235,7 @@
         <v>45007</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>46181</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>46181</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13564,7 +13564,7 @@
         <v>45191</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13669,7 +13669,7 @@
         <v>44572</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13779,7 +13779,7 @@
         <v>46209</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13889,7 +13889,7 @@
         <v>44637</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13999,7 +13999,7 @@
         <v>45740</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14109,7 +14109,7 @@
         <v>45163</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44774</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14319,7 +14319,7 @@
         <v>44854</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14424,7 +14424,7 @@
         <v>45343</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45222</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14634,7 +14634,7 @@
         <v>44953</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14739,7 +14739,7 @@
         <v>44637</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14848,7 +14848,7 @@
         <v>45586</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>44518</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>45105</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>45141</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>44911</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45140</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45643</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45211</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>45540</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45350</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15908,7 +15908,7 @@
         <v>45182</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16013,7 +16013,7 @@
         <v>45156</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>45624</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>44501</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44724</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16484,7 +16484,7 @@
         <v>44536</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>44614</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16630,7 +16630,7 @@
         <v>44535</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16703,7 +16703,7 @@
         <v>44722</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16781,7 +16781,7 @@
         <v>44869</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16859,7 +16859,7 @@
         <v>44473</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16932,7 +16932,7 @@
         <v>44608</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -17010,7 +17010,7 @@
         <v>44752</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>44720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17161,7 +17161,7 @@
         <v>44873</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17234,7 +17234,7 @@
         <v>44769</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17307,7 +17307,7 @@
         <v>44745</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17380,7 +17380,7 @@
         <v>44839</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17453,7 +17453,7 @@
         <v>44579</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17526,7 +17526,7 @@
         <v>44807</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17599,7 +17599,7 @@
         <v>44855</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17672,7 +17672,7 @@
         <v>44879</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17745,7 +17745,7 @@
         <v>44739</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17818,7 +17818,7 @@
         <v>44770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17896,7 +17896,7 @@
         <v>44769</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17969,7 +17969,7 @@
         <v>44640</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18042,7 +18042,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18115,7 +18115,7 @@
         <v>44725</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>44643</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>44474</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>44778</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18412,7 +18412,7 @@
         <v>44588</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18485,7 +18485,7 @@
         <v>44769</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18558,7 +18558,7 @@
         <v>44839</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>44886</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18704,7 +18704,7 @@
         <v>44854</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18777,7 +18777,7 @@
         <v>44697</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18850,7 +18850,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18928,7 +18928,7 @@
         <v>44769</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>44846</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>44636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19152,7 +19152,7 @@
         <v>44752</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19225,7 +19225,7 @@
         <v>44752</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>44566</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19376,7 +19376,7 @@
         <v>44862</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19449,7 +19449,7 @@
         <v>44610</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44643</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>44705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>44636</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>44818</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45720</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45311</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20038,7 +20038,7 @@
         <v>44741</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20111,7 +20111,7 @@
         <v>45358</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20184,7 +20184,7 @@
         <v>45228</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>44862</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45222</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20408,7 +20408,7 @@
         <v>45330</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45398</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45250</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45441</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>44796</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20856,7 +20856,7 @@
         <v>45257</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20929,7 +20929,7 @@
         <v>45114</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -21002,7 +21002,7 @@
         <v>44887</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>45119</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>44517</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21221,7 +21221,7 @@
         <v>45322</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21294,7 +21294,7 @@
         <v>45555</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21367,7 +21367,7 @@
         <v>45256</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45610</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>45883</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21586,7 +21586,7 @@
         <v>45798</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>45797</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>45798</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>45798</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21883,7 +21883,7 @@
         <v>45798</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21956,7 +21956,7 @@
         <v>44887</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45478</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22180,7 +22180,7 @@
         <v>45702</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45632</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22326,7 +22326,7 @@
         <v>45176</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22399,7 +22399,7 @@
         <v>44522</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22472,7 +22472,7 @@
         <v>45540</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22545,7 +22545,7 @@
         <v>46044</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22618,7 +22618,7 @@
         <v>45161</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44636</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44859</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45280</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22915,7 +22915,7 @@
         <v>46056</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22988,7 +22988,7 @@
         <v>46044</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>44896</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23222,7 +23222,7 @@
         <v>44616</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23295,7 +23295,7 @@
         <v>45014</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23373,7 +23373,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23446,7 +23446,7 @@
         <v>46071</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44588</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23592,7 +23592,7 @@
         <v>44838</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23665,7 +23665,7 @@
         <v>44958</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23743,7 +23743,7 @@
         <v>45926</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>46077</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45226</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23967,7 +23967,7 @@
         <v>46079</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>46079</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>46079</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24201,7 +24201,7 @@
         <v>46082</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24274,7 +24274,7 @@
         <v>46080</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>46080</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24430,7 +24430,7 @@
         <v>45244</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24503,7 +24503,7 @@
         <v>46080</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24581,7 +24581,7 @@
         <v>45932</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24659,7 +24659,7 @@
         <v>46083</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24737,7 +24737,7 @@
         <v>45166</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24810,7 +24810,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24883,7 +24883,7 @@
         <v>45933</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24961,7 +24961,7 @@
         <v>44524</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25034,7 +25034,7 @@
         <v>44897</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25112,7 +25112,7 @@
         <v>45209</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25185,7 +25185,7 @@
         <v>44986</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>44988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25336,7 +25336,7 @@
         <v>44778</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25409,7 +25409,7 @@
         <v>45089</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45946</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25555,7 +25555,7 @@
         <v>45448</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25628,7 +25628,7 @@
         <v>45888</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25701,7 +25701,7 @@
         <v>45553</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>46108</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25852,7 +25852,7 @@
         <v>45684</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25925,7 +25925,7 @@
         <v>46112</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>46113</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26071,7 +26071,7 @@
         <v>44911</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26149,7 +26149,7 @@
         <v>45581</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26222,7 +26222,7 @@
         <v>44761</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26295,7 +26295,7 @@
         <v>45636</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26368,7 +26368,7 @@
         <v>46125</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45964</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26519,7 +26519,7 @@
         <v>45964</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26592,7 +26592,7 @@
         <v>46126</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26665,7 +26665,7 @@
         <v>44970</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>44722</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>44722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26884,7 +26884,7 @@
         <v>45817</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26962,7 +26962,7 @@
         <v>46126</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27035,7 +27035,7 @@
         <v>46126</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27108,7 +27108,7 @@
         <v>45974</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27181,7 +27181,7 @@
         <v>46129</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27254,7 +27254,7 @@
         <v>46132</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27332,7 +27332,7 @@
         <v>46121</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27405,7 +27405,7 @@
         <v>46121</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>46121</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>46132</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27629,7 +27629,7 @@
         <v>45012</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27707,7 +27707,7 @@
         <v>46134</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27780,7 +27780,7 @@
         <v>45713</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45805</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45597</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27999,7 +27999,7 @@
         <v>45632</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45993</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45994</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45994</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28301,7 +28301,7 @@
         <v>45993</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28374,7 +28374,7 @@
         <v>45993</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28447,7 +28447,7 @@
         <v>45895</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>45995</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45995</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>44807</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>45225</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28817,7 +28817,7 @@
         <v>46000</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28895,7 +28895,7 @@
         <v>45225</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28968,7 +28968,7 @@
         <v>45030</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45713</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29114,7 +29114,7 @@
         <v>45869</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29187,7 +29187,7 @@
         <v>45888</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>45228</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29333,7 +29333,7 @@
         <v>45974</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29406,7 +29406,7 @@
         <v>45718</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>44522</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45211</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29630,7 +29630,7 @@
         <v>45048</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45671</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29776,7 +29776,7 @@
         <v>45007</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29849,7 +29849,7 @@
         <v>45345</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29922,7 +29922,7 @@
         <v>45082</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29995,7 +29995,7 @@
         <v>44909</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30073,7 +30073,7 @@
         <v>45041</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30146,7 +30146,7 @@
         <v>45791</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45993</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30292,7 +30292,7 @@
         <v>44979</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30365,7 +30365,7 @@
         <v>45068</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30443,7 +30443,7 @@
         <v>44848</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30521,7 +30521,7 @@
         <v>45225</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>45830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30667,7 +30667,7 @@
         <v>45830</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30740,7 +30740,7 @@
         <v>44864</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30813,7 +30813,7 @@
         <v>45216</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30891,7 +30891,7 @@
         <v>45555</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>44466</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31037,7 +31037,7 @@
         <v>45740</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31115,7 +31115,7 @@
         <v>45224</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31193,7 +31193,7 @@
         <v>45260</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31266,7 +31266,7 @@
         <v>45271</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31339,7 +31339,7 @@
         <v>45103</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45022</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45034</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31558,7 +31558,7 @@
         <v>45104</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31631,7 +31631,7 @@
         <v>46069</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31704,7 +31704,7 @@
         <v>45081</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31777,7 +31777,7 @@
         <v>45081</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45001</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31928,7 +31928,7 @@
         <v>46168</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -32001,7 +32001,7 @@
         <v>46168</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32079,7 +32079,7 @@
         <v>45702</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32152,7 +32152,7 @@
         <v>46168</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32225,7 +32225,7 @@
         <v>46168</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32303,7 +32303,7 @@
         <v>45729</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32376,7 +32376,7 @@
         <v>45147</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32449,7 +32449,7 @@
         <v>46168</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>46168</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>44553</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32678,7 +32678,7 @@
         <v>46170</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32751,7 +32751,7 @@
         <v>44909</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32829,7 +32829,7 @@
         <v>46121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32902,7 +32902,7 @@
         <v>45618</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>46170</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33073,7 +33073,7 @@
         <v>45250</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33151,7 +33151,7 @@
         <v>45161</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33224,7 +33224,7 @@
         <v>44899</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33297,7 +33297,7 @@
         <v>45932</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>46175</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33443,7 +33443,7 @@
         <v>46175</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33516,7 +33516,7 @@
         <v>45163</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33589,7 +33589,7 @@
         <v>44980</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>44473</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33735,7 +33735,7 @@
         <v>46176</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33813,7 +33813,7 @@
         <v>44991</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33886,7 +33886,7 @@
         <v>44957</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33959,7 +33959,7 @@
         <v>44614</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34032,7 +34032,7 @@
         <v>45180</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45528</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34178,7 +34178,7 @@
         <v>46181</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34251,7 +34251,7 @@
         <v>46181</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34324,7 +34324,7 @@
         <v>46181</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34402,7 +34402,7 @@
         <v>46183</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>44544</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34553,7 +34553,7 @@
         <v>45175</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34626,7 +34626,7 @@
         <v>46170</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34704,7 +34704,7 @@
         <v>45163</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34777,7 +34777,7 @@
         <v>44495</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34850,7 +34850,7 @@
         <v>46185</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>46185</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34996,7 +34996,7 @@
         <v>45327</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35069,7 +35069,7 @@
         <v>46188</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35142,7 +35142,7 @@
         <v>46188</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35215,7 +35215,7 @@
         <v>46188</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35288,7 +35288,7 @@
         <v>45161</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>46196</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>44610</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35507,7 +35507,7 @@
         <v>45880</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35580,7 +35580,7 @@
         <v>44602</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35653,7 +35653,7 @@
         <v>45114</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35726,7 +35726,7 @@
         <v>45328</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35799,7 +35799,7 @@
         <v>45555</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35872,7 +35872,7 @@
         <v>46205</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35945,7 +35945,7 @@
         <v>45166</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36018,7 +36018,7 @@
         <v>46251</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36096,7 +36096,7 @@
         <v>46250</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>46251</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36247,7 +36247,7 @@
         <v>46251</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36325,7 +36325,7 @@
         <v>44531</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36398,7 +36398,7 @@
         <v>46253</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36471,7 +36471,7 @@
         <v>44634</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45189</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36622,7 +36622,7 @@
         <v>46258</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36700,7 +36700,7 @@
         <v>46258</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36778,7 +36778,7 @@
         <v>46258</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36856,7 +36856,7 @@
         <v>45209</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36929,7 +36929,7 @@
         <v>46198</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -37002,7 +37002,7 @@
         <v>44614</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44676</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>45454</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37221,7 +37221,7 @@
         <v>45740</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37299,7 +37299,7 @@
         <v>44785</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37372,7 +37372,7 @@
         <v>45230</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37445,7 +37445,7 @@
         <v>44846</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37523,7 +37523,7 @@
         <v>46252</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37596,7 +37596,7 @@
         <v>46252</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37669,7 +37669,7 @@
         <v>44819</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37742,7 +37742,7 @@
         <v>46252</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>45057</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37888,7 +37888,7 @@
         <v>45169</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37961,7 +37961,7 @@
         <v>44733</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38034,7 +38034,7 @@
         <v>44907</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38107,7 +38107,7 @@
         <v>45315</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>46266</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38258,7 +38258,7 @@
         <v>46265</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38331,7 +38331,7 @@
         <v>44887</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38404,7 +38404,7 @@
         <v>45378</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38482,7 +38482,7 @@
         <v>46267</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38560,7 +38560,7 @@
         <v>45163</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>46267</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38711,7 +38711,7 @@
         <v>46267</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45250</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38862,7 +38862,7 @@
         <v>46229</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38935,7 +38935,7 @@
         <v>45321</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -39008,7 +39008,7 @@
         <v>46273</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39086,7 +39086,7 @@
         <v>44900</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>46273</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39237,7 +39237,7 @@
         <v>46273</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>45309</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39388,7 +39388,7 @@
         <v>44958</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39461,7 +39461,7 @@
         <v>44868</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39539,7 +39539,7 @@
         <v>44624</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39612,7 +39612,7 @@
         <v>44624</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45411</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39758,7 +39758,7 @@
         <v>44970</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>44896</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>45244</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39992,7 +39992,7 @@
         <v>46240</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40065,7 +40065,7 @@
         <v>45531</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40138,7 +40138,7 @@
         <v>44859</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40216,7 +40216,7 @@
         <v>45501</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40289,7 +40289,7 @@
         <v>46244</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>46091</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40435,7 +40435,7 @@
         <v>46283</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40508,7 +40508,7 @@
         <v>44566</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40581,7 +40581,7 @@
         <v>46249</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40654,7 +40654,7 @@
         <v>44960</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40727,7 +40727,7 @@
         <v>46286</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40800,7 +40800,7 @@
         <v>44855</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40873,7 +40873,7 @@
         <v>44855</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40946,7 +40946,7 @@
         <v>45140</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -41019,7 +41019,7 @@
         <v>45072</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41092,7 +41092,7 @@
         <v>45482</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41165,7 +41165,7 @@
         <v>45213</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41243,7 +41243,7 @@
         <v>45510</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41316,7 +41316,7 @@
         <v>44914</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41389,7 +41389,7 @@
         <v>44785</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>44648</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41535,7 +41535,7 @@
         <v>44979</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41608,7 +41608,7 @@
         <v>45056</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41681,7 +41681,7 @@
         <v>44739</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41754,7 +41754,7 @@
         <v>44769</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41827,7 +41827,7 @@
         <v>45036</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44872</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41973,7 +41973,7 @@
         <v>45239</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>45244</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>44701</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42197,7 +42197,7 @@
         <v>45270</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45161</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42343,7 +42343,7 @@
         <v>45518</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45574</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42494,7 +42494,7 @@
         <v>45365</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42567,7 +42567,7 @@
         <v>45299</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42640,7 +42640,7 @@
         <v>45299</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45022</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42786,7 +42786,7 @@
         <v>45110</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42859,7 +42859,7 @@
         <v>45149</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42937,7 +42937,7 @@
         <v>45555</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -43010,7 +43010,7 @@
         <v>45331</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43083,7 +43083,7 @@
         <v>45140</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43161,7 +43161,7 @@
         <v>44931</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43239,7 +43239,7 @@
         <v>44580</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43312,7 +43312,7 @@
         <v>45217</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43390,7 +43390,7 @@
         <v>45066</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43463,7 +43463,7 @@
         <v>44907</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43536,7 +43536,7 @@
         <v>45667</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43609,7 +43609,7 @@
         <v>45230</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45230</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43755,7 +43755,7 @@
         <v>45013</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43828,7 +43828,7 @@
         <v>45566</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43901,7 +43901,7 @@
         <v>45244</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43979,7 +43979,7 @@
         <v>45386</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44052,7 +44052,7 @@
         <v>45777</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44130,7 +44130,7 @@
         <v>45350</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44203,7 +44203,7 @@
         <v>45252</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44276,7 +44276,7 @@
         <v>45008</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44349,7 +44349,7 @@
         <v>44852</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44422,7 +44422,7 @@
         <v>44883</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44495,7 +44495,7 @@
         <v>45414</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45790</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44641,7 +44641,7 @@
         <v>45790</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44714,7 +44714,7 @@
         <v>45790</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44787,7 +44787,7 @@
         <v>44588</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44860,7 +44860,7 @@
         <v>44685</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44938,7 +44938,7 @@
         <v>44964</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45686</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45089,7 +45089,7 @@
         <v>44742</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>45446</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -45235,7 +45235,7 @@
         <v>45403</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>46164</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45039</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44956</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>46097</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44814</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44472</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45212</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>46071</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45946</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45666</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44790</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45142</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44830</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44637</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46068</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>45838</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44865</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45400</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44474</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45219</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44971</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>46106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45211</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45068</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>44907</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45166</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44848</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44785</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44624</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44986</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44697</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44746</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44503</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44608</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44838</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44735</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44881</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45007</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46056</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45540</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45348</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46071</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>46079</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45182</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44518</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44572</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45156</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>46149</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46209</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44495</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44865</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45350</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>46294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44854</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45211</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44501</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44724</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44536</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44535</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44722</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44869</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44473</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44608</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44752</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44720</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44873</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44769</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44745</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44839</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44579</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44807</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44855</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44879</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44739</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44769</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44640</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44725</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44643</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44778</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44839</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44886</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44854</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44846</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44752</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44752</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44566</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44862</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44610</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44643</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44636</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>44818</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>44980</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45378</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44531</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45531</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45555</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44785</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44914</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44544</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44495</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44473</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45068</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45510</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45225</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44796</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45482</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45597</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>45226</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45790</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45790</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45270</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44970</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45166</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45149</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44733</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44522</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45610</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45555</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45797</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46044</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45798</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45798</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45702</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45798</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45798</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45147</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45926</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46044</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44859</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44624</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45933</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45311</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44588</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45299</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44872</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45888</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45946</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44859</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>46080</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46080</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>46079</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46079</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>46079</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>46080</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>46082</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46083</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45228</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45684</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45034</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45964</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44602</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45398</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45089</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45974</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45667</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44761</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>46108</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45581</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45260</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44838</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46112</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45358</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45993</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45993</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45993</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>44722</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44722</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46125</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44785</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45995</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46126</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46121</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>46121</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44616</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>46121</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45830</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>46132</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45830</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46132</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45553</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45103</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45213</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45888</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45805</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45104</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45718</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45322</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45280</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44862</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44524</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44522</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45411</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45555</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45702</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45729</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45081</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45081</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45228</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45022</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45632</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45022</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44897</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44778</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45895</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45869</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44807</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45331</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45066</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44979</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45330</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44864</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44855</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45791</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45250</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45250</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>44855</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44899</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45993</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45528</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44896</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44970</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45140</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45713</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45209</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45244</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45224</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44991</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45048</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45056</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45230</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45119</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46168</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46168</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46168</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46168</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>44624</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>46121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46170</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45618</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45883</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45932</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>46175</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46176</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>46181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45041</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45166</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44701</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45740</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44909</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>46181</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45518</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45271</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46170</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>46185</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45257</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45632</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45315</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45321</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46188</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>44676</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45013</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45230</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46196</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44741</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>44636</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44887</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45161</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44911</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46258</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46258</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45012</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44887</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44958</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46265</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46266</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44907</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44900</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46267</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45072</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45217</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45114</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45299</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45082</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46273</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46229</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>46273</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44887</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45169</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45225</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45501</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45555</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45161</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45250</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46240</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45211</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46283</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45225</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>46091</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44848</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45441</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>46286</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44614</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46244</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45720</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45540</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44614</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>46250</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>46175</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>44909</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>46293</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45327</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45001</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>46249</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>44553</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46251</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46252</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45345</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46253</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>46251</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46251</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>46252</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>46205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44648</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44739</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45454</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45478</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46296</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45713</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44580</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45140</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>44819</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44769</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45110</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45250</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44960</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45244</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45328</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>44907</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45365</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45244</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>44634</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45180</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45256</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45007</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45448</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45386</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44610</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45014</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45671</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44958</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45777</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45414</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45350</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>44883</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>44852</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45686</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>44742</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44588</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>44685</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45446</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45403</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>46164</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45039</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3888,7 +3888,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4002,7 +4002,7 @@
         <v>44956</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4111,7 +4111,7 @@
         <v>46097</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>46119</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>44814</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4446,7 +4446,7 @@
         <v>45714</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4560,7 +4560,7 @@
         <v>44596</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>44472</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>46044</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>45212</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>45518</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44986</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5439,7 +5439,7 @@
         <v>45777</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5552,7 +5552,7 @@
         <v>44771</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5659,7 +5659,7 @@
         <v>46071</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5766,7 +5766,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5873,7 +5873,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5984,7 +5984,7 @@
         <v>45946</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>46119</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6203,7 +6203,7 @@
         <v>45789</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6310,7 +6310,7 @@
         <v>45965</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6417,7 +6417,7 @@
         <v>45883</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6524,7 +6524,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6640,7 +6640,7 @@
         <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45272</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6854,7 +6854,7 @@
         <v>45666</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>44790</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45142</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>45275</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7314,7 +7314,7 @@
         <v>44830</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7421,7 +7421,7 @@
         <v>45530</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7528,7 +7528,7 @@
         <v>44637</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7638,7 +7638,7 @@
         <v>44624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7744,7 +7744,7 @@
         <v>44715</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7855,7 +7855,7 @@
         <v>46044</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
         <v>45798</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8077,7 +8077,7 @@
         <v>46068</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8183,7 +8183,7 @@
         <v>45838</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>44826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8395,7 +8395,7 @@
         <v>44865</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>45400</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8616,7 +8616,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8722,7 +8722,7 @@
         <v>44474</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45219</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44971</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>46106</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
         <v>45211</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9256,7 +9256,7 @@
         <v>45068</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>46258</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>44907</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9579,7 +9579,7 @@
         <v>44596</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45166</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>44848</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9907,7 +9907,7 @@
         <v>46155</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44785</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10119,7 +10119,7 @@
         <v>44624</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10225,7 +10225,7 @@
         <v>44986</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44697</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
         <v>44746</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10546,7 +10546,7 @@
         <v>44503</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10651,7 +10651,7 @@
         <v>44608</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10761,7 +10761,7 @@
         <v>44838</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10866,7 +10866,7 @@
         <v>44735</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>45140</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11076,7 +11076,7 @@
         <v>45510</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44881</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11286,7 +11286,7 @@
         <v>45624</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11391,7 +11391,7 @@
         <v>45007</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>46035</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
         <v>46035</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11725,7 +11725,7 @@
         <v>46056</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>45540</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11935,7 +11935,7 @@
         <v>45931</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12045,7 +12045,7 @@
         <v>45348</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12150,7 +12150,7 @@
         <v>44774</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12255,7 +12255,7 @@
         <v>46071</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12365,7 +12365,7 @@
         <v>45740</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>46079</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12585,7 +12585,7 @@
         <v>45954</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12695,7 +12695,7 @@
         <v>45343</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12800,7 +12800,7 @@
         <v>45182</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45141</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13010,7 +13010,7 @@
         <v>44518</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44572</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13225,7 +13225,7 @@
         <v>45740</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13335,7 +13335,7 @@
         <v>45156</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13445,7 +13445,7 @@
         <v>46149</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13550,7 +13550,7 @@
         <v>45643</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13655,7 +13655,7 @@
         <v>45222</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>46168</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13870,7 +13870,7 @@
         <v>46181</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>46181</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14089,7 +14089,7 @@
         <v>45586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14194,7 +14194,7 @@
         <v>44624</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45163</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14404,7 +14404,7 @@
         <v>44637</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>46209</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44911</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14734,7 +14734,7 @@
         <v>44953</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14948,7 +14948,7 @@
         <v>45105</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15058,7 +15058,7 @@
         <v>44495</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44865</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15278,7 +15278,7 @@
         <v>45350</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15383,7 +15383,7 @@
         <v>45377</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>46294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>44854</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15698,7 +15698,7 @@
         <v>44503</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15803,7 +15803,7 @@
         <v>45740</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45211</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>45191</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16123,7 +16123,7 @@
         <v>45196</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44501</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>44724</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>44536</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44614</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>44535</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16598,7 +16598,7 @@
         <v>44722</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>44869</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44473</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         <v>44608</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>44752</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16978,7 +16978,7 @@
         <v>44720</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -17056,7 +17056,7 @@
         <v>44873</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17129,7 +17129,7 @@
         <v>44769</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17202,7 +17202,7 @@
         <v>44745</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17275,7 +17275,7 @@
         <v>44839</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17348,7 +17348,7 @@
         <v>44579</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17421,7 +17421,7 @@
         <v>44807</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17494,7 +17494,7 @@
         <v>44855</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17567,7 +17567,7 @@
         <v>44879</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17640,7 +17640,7 @@
         <v>44739</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17713,7 +17713,7 @@
         <v>44770</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17791,7 +17791,7 @@
         <v>44769</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17864,7 +17864,7 @@
         <v>44640</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17937,7 +17937,7 @@
         <v>44725</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>44830</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44643</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>44474</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>44778</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18307,7 +18307,7 @@
         <v>44588</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>44769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>44839</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18526,7 +18526,7 @@
         <v>44886</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18599,7 +18599,7 @@
         <v>44854</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18672,7 +18672,7 @@
         <v>44697</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18745,7 +18745,7 @@
         <v>44769</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18818,7 +18818,7 @@
         <v>44578</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18896,7 +18896,7 @@
         <v>44846</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18974,7 +18974,7 @@
         <v>44636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -19047,7 +19047,7 @@
         <v>44752</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19120,7 +19120,7 @@
         <v>44752</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>44566</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19271,7 +19271,7 @@
         <v>44862</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>44610</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         <v>44643</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19495,7 +19495,7 @@
         <v>44636</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44705</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19641,7 +19641,7 @@
         <v>44818</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19714,7 +19714,7 @@
         <v>44980</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19787,7 +19787,7 @@
         <v>44868</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19865,7 +19865,7 @@
         <v>45378</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19943,7 +19943,7 @@
         <v>44531</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45531</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -20089,7 +20089,7 @@
         <v>44517</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20162,7 +20162,7 @@
         <v>45555</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20235,7 +20235,7 @@
         <v>44785</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20308,7 +20308,7 @@
         <v>44986</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44914</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20454,7 +20454,7 @@
         <v>44544</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20527,7 +20527,7 @@
         <v>45008</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20600,7 +20600,7 @@
         <v>44495</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20673,7 +20673,7 @@
         <v>44473</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45636</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20819,7 +20819,7 @@
         <v>45068</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20897,7 +20897,7 @@
         <v>45510</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20970,7 +20970,7 @@
         <v>45225</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -21043,7 +21043,7 @@
         <v>44796</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21116,7 +21116,7 @@
         <v>45790</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>45482</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21262,7 +21262,7 @@
         <v>45239</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21340,7 +21340,7 @@
         <v>45597</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21413,7 +21413,7 @@
         <v>45226</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21486,7 +21486,7 @@
         <v>45790</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45790</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21632,7 +21632,7 @@
         <v>45270</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21705,7 +21705,7 @@
         <v>44970</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>45166</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21856,7 +21856,7 @@
         <v>45149</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21934,7 +21934,7 @@
         <v>45309</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -22007,7 +22007,7 @@
         <v>44733</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22080,7 +22080,7 @@
         <v>46036</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22158,7 +22158,7 @@
         <v>45209</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22231,7 +22231,7 @@
         <v>44522</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22309,7 +22309,7 @@
         <v>45610</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22382,7 +22382,7 @@
         <v>45555</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45797</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22528,7 +22528,7 @@
         <v>46044</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>44931</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22679,7 +22679,7 @@
         <v>45798</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22752,7 +22752,7 @@
         <v>45798</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22825,7 +22825,7 @@
         <v>45702</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22898,7 +22898,7 @@
         <v>45798</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22971,7 +22971,7 @@
         <v>45798</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -23049,7 +23049,7 @@
         <v>44979</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23122,7 +23122,7 @@
         <v>45924</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23200,7 +23200,7 @@
         <v>46056</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23273,7 +23273,7 @@
         <v>45147</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45926</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23424,7 +23424,7 @@
         <v>46044</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23502,7 +23502,7 @@
         <v>44859</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45244</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>44624</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45163</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45740</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23877,7 +23877,7 @@
         <v>45933</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23955,7 +23955,7 @@
         <v>45932</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -24033,7 +24033,7 @@
         <v>46071</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>46071</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45311</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44588</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24325,7 +24325,7 @@
         <v>45299</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24398,7 +24398,7 @@
         <v>44896</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>44872</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24549,7 +24549,7 @@
         <v>45888</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24622,7 +24622,7 @@
         <v>45946</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46077</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>44859</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24846,7 +24846,7 @@
         <v>46080</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>46080</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -25002,7 +25002,7 @@
         <v>46079</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -25080,7 +25080,7 @@
         <v>46079</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>46079</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25236,7 +25236,7 @@
         <v>45057</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25309,7 +25309,7 @@
         <v>46080</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25387,7 +25387,7 @@
         <v>46082</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25460,7 +25460,7 @@
         <v>46083</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25538,7 +25538,7 @@
         <v>45228</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>45684</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25684,7 +25684,7 @@
         <v>45034</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25757,7 +25757,7 @@
         <v>45964</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>45964</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25903,7 +25903,7 @@
         <v>45817</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25981,7 +25981,7 @@
         <v>44602</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>45398</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26127,7 +26127,7 @@
         <v>45089</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26200,7 +26200,7 @@
         <v>45974</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26273,7 +26273,7 @@
         <v>45667</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26346,7 +26346,7 @@
         <v>44761</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26419,7 +26419,7 @@
         <v>46108</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26497,7 +26497,7 @@
         <v>45566</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45581</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26643,7 +26643,7 @@
         <v>45260</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26716,7 +26716,7 @@
         <v>44838</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>46112</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26862,7 +26862,7 @@
         <v>46113</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45358</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45993</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -27081,7 +27081,7 @@
         <v>45993</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27154,7 +27154,7 @@
         <v>45993</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27227,7 +27227,7 @@
         <v>44722</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27300,7 +27300,7 @@
         <v>44722</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>46126</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27446,7 +27446,7 @@
         <v>46126</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>46125</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45994</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>44785</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45995</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27821,7 +27821,7 @@
         <v>46126</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27894,7 +27894,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27972,7 +27972,7 @@
         <v>46121</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -28045,7 +28045,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28123,7 +28123,7 @@
         <v>46121</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28196,7 +28196,7 @@
         <v>44616</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28269,7 +28269,7 @@
         <v>46129</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28342,7 +28342,7 @@
         <v>46121</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28415,7 +28415,7 @@
         <v>45830</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28488,7 +28488,7 @@
         <v>46000</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>46132</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28644,7 +28644,7 @@
         <v>45830</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28717,7 +28717,7 @@
         <v>46132</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28795,7 +28795,7 @@
         <v>45553</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28868,7 +28868,7 @@
         <v>45103</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28941,7 +28941,7 @@
         <v>45213</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45888</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>45805</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45104</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29238,7 +29238,7 @@
         <v>45718</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29311,7 +29311,7 @@
         <v>45322</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29384,7 +29384,7 @@
         <v>45280</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29457,7 +29457,7 @@
         <v>44862</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29535,7 +29535,7 @@
         <v>44524</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29608,7 +29608,7 @@
         <v>44522</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45411</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29754,7 +29754,7 @@
         <v>44979</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29827,7 +29827,7 @@
         <v>45555</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29900,7 +29900,7 @@
         <v>45702</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45974</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45729</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30119,7 +30119,7 @@
         <v>45081</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30192,7 +30192,7 @@
         <v>45081</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30265,7 +30265,7 @@
         <v>44988</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45228</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30416,7 +30416,7 @@
         <v>45022</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30489,7 +30489,7 @@
         <v>45632</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30562,7 +30562,7 @@
         <v>45022</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30635,7 +30635,7 @@
         <v>44897</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30713,7 +30713,7 @@
         <v>44778</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30786,7 +30786,7 @@
         <v>45895</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30859,7 +30859,7 @@
         <v>45869</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>44807</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -31005,7 +31005,7 @@
         <v>45331</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45066</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31151,7 +31151,7 @@
         <v>44979</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31224,7 +31224,7 @@
         <v>45330</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31302,7 +31302,7 @@
         <v>44864</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31375,7 +31375,7 @@
         <v>44855</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31448,7 +31448,7 @@
         <v>45791</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31521,7 +31521,7 @@
         <v>45250</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>45250</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31672,7 +31672,7 @@
         <v>44855</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31745,7 +31745,7 @@
         <v>44899</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>45993</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31891,7 +31891,7 @@
         <v>45528</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44896</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>44970</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>45140</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>45713</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>44957</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>45209</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45244</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32485,7 +32485,7 @@
         <v>45224</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32563,7 +32563,7 @@
         <v>44991</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32636,7 +32636,7 @@
         <v>45048</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46069</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>45056</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>45574</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32933,7 +32933,7 @@
         <v>45230</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45119</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -33079,7 +33079,7 @@
         <v>44566</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33152,7 +33152,7 @@
         <v>46168</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33230,7 +33230,7 @@
         <v>46168</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33381,7 +33381,7 @@
         <v>46168</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33454,7 +33454,7 @@
         <v>46168</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33532,7 +33532,7 @@
         <v>46168</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>46168</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33683,7 +33683,7 @@
         <v>44624</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33756,7 +33756,7 @@
         <v>46121</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33829,7 +33829,7 @@
         <v>46170</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>46170</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -34000,7 +34000,7 @@
         <v>45618</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -34073,7 +34073,7 @@
         <v>45883</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>45932</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>46175</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34292,7 +34292,7 @@
         <v>46176</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>46181</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34443,7 +34443,7 @@
         <v>46181</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34516,7 +34516,7 @@
         <v>45041</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34589,7 +34589,7 @@
         <v>45222</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45166</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34735,7 +34735,7 @@
         <v>44701</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34808,7 +34808,7 @@
         <v>45740</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>44909</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>46181</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -35042,7 +35042,7 @@
         <v>45518</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35115,7 +35115,7 @@
         <v>45271</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35188,7 +35188,7 @@
         <v>46170</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35266,7 +35266,7 @@
         <v>46185</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45257</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35412,7 +35412,7 @@
         <v>45632</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35485,7 +35485,7 @@
         <v>46183</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35563,7 +35563,7 @@
         <v>46188</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45315</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35709,7 +35709,7 @@
         <v>45321</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>46188</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35855,7 +35855,7 @@
         <v>46188</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35928,7 +35928,7 @@
         <v>44676</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -36001,7 +36001,7 @@
         <v>45013</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -36074,7 +36074,7 @@
         <v>45230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36147,7 +36147,7 @@
         <v>45230</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36220,7 +36220,7 @@
         <v>46196</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45163</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36366,7 +36366,7 @@
         <v>44741</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36439,7 +36439,7 @@
         <v>44636</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36512,7 +36512,7 @@
         <v>44887</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36585,7 +36585,7 @@
         <v>45161</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36658,7 +36658,7 @@
         <v>44911</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36736,7 +36736,7 @@
         <v>46258</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36814,7 +36814,7 @@
         <v>46258</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36892,7 +36892,7 @@
         <v>45114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36965,7 +36965,7 @@
         <v>46258</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -37043,7 +37043,7 @@
         <v>45161</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37116,7 +37116,7 @@
         <v>45012</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>44887</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37267,7 +37267,7 @@
         <v>44958</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37340,7 +37340,7 @@
         <v>46265</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37413,7 +37413,7 @@
         <v>46266</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37491,7 +37491,7 @@
         <v>44907</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44900</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37637,7 +37637,7 @@
         <v>46267</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>45072</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37788,7 +37788,7 @@
         <v>46267</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>46267</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37944,7 +37944,7 @@
         <v>45217</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -38022,7 +38022,7 @@
         <v>45114</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -38095,7 +38095,7 @@
         <v>45299</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38168,7 +38168,7 @@
         <v>46273</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38246,7 +38246,7 @@
         <v>45189</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38324,7 +38324,7 @@
         <v>45082</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46273</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45030</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38548,7 +38548,7 @@
         <v>46229</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38621,7 +38621,7 @@
         <v>46273</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38699,7 +38699,7 @@
         <v>44887</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38772,7 +38772,7 @@
         <v>45169</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38845,7 +38845,7 @@
         <v>45225</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45501</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>45555</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39142,7 +39142,7 @@
         <v>45161</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45250</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39293,7 +39293,7 @@
         <v>46240</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39366,7 +39366,7 @@
         <v>45211</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39439,7 +39439,7 @@
         <v>46283</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39512,7 +39512,7 @@
         <v>45225</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39585,7 +39585,7 @@
         <v>46091</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39658,7 +39658,7 @@
         <v>44848</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39736,7 +39736,7 @@
         <v>45441</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39809,7 +39809,7 @@
         <v>46286</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39882,7 +39882,7 @@
         <v>44614</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39955,7 +39955,7 @@
         <v>46244</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45720</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -40101,7 +40101,7 @@
         <v>45230</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45540</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>44614</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>46250</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>46175</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>44909</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40544,7 +40544,7 @@
         <v>46293</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>45327</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40695,7 +40695,7 @@
         <v>45001</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40773,7 +40773,7 @@
         <v>46249</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40846,7 +40846,7 @@
         <v>44553</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40919,7 +40919,7 @@
         <v>46251</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40997,7 +40997,7 @@
         <v>46252</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -41070,7 +41070,7 @@
         <v>45345</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41143,7 +41143,7 @@
         <v>46253</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41216,7 +41216,7 @@
         <v>46251</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41294,7 +41294,7 @@
         <v>46251</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>46252</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>46205</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41518,7 +41518,7 @@
         <v>44648</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41591,7 +41591,7 @@
         <v>44739</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41664,7 +41664,7 @@
         <v>46295</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>45454</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41810,7 +41810,7 @@
         <v>45478</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41883,7 +41883,7 @@
         <v>46296</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41956,7 +41956,7 @@
         <v>45713</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -42029,7 +42029,7 @@
         <v>44580</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -42102,7 +42102,7 @@
         <v>45140</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42180,7 +42180,7 @@
         <v>44819</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42253,7 +42253,7 @@
         <v>44769</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45110</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42399,7 +42399,7 @@
         <v>45250</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42472,7 +42472,7 @@
         <v>45161</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
         <v>44960</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45244</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42696,7 +42696,7 @@
         <v>45328</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42769,7 +42769,7 @@
         <v>45175</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42842,7 +42842,7 @@
         <v>45036</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42915,7 +42915,7 @@
         <v>44907</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42988,7 +42988,7 @@
         <v>45365</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -43061,7 +43061,7 @@
         <v>45244</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>44634</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43207,7 +43207,7 @@
         <v>45176</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43280,7 +43280,7 @@
         <v>45216</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43358,7 +43358,7 @@
         <v>45180</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45256</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43504,7 +43504,7 @@
         <v>45007</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43577,7 +43577,7 @@
         <v>45448</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43650,7 +43650,7 @@
         <v>45386</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43723,7 +43723,7 @@
         <v>44610</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43796,7 +43796,7 @@
         <v>45014</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45671</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43947,7 +43947,7 @@
         <v>45163</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>44958</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -44098,7 +44098,7 @@
         <v>45777</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45414</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44249,7 +44249,7 @@
         <v>45252</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -44322,7 +44322,7 @@
         <v>45350</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -44395,7 +44395,7 @@
         <v>44883</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>44852</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>44964</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -44619,7 +44619,7 @@
         <v>45686</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -44692,7 +44692,7 @@
         <v>44742</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44588</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -44838,7 +44838,7 @@
         <v>44685</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -44916,7 +44916,7 @@
         <v>45446</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -44989,7 +44989,7 @@
         <v>45403</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -45062,7 +45062,7 @@
         <v>46164</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45323</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44624</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45039</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46108</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46079</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45209</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44956</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45600</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45714</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45518</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46044</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44724</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45272</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44771</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45666</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>44790</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44971</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45068</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45211</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45838</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44907</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44848</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>46044</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44697</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44503</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44608</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44911</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45211</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45540</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44495</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45377</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45156</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45007</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45196</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45740</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45191</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45740</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44785</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44774</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44854</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45510</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45343</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44637</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44518</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>46071</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>46079</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>46168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>46209</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44722</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44535</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44869</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44752</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44745</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44879</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44643</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44739</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44636</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>44578</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44778</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44752</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44752</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>44769</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44769</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>44846</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44566</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44640</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44839</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44725</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44854</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44610</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44643</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45225</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44697</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44705</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44818</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45222</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44872</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44864</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45216</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45250</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45555</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45250</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45311</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45358</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45740</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44741</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45228</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45260</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45398</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45271</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45103</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45441</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45244</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44862</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>44701</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45022</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45270</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45114</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45104</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45574</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45119</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45081</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45081</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44887</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45365</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45299</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45299</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45022</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45147</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44517</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45110</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45322</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45555</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44553</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45331</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45066</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45163</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44907</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>44980</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>44887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45478</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45230</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45230</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45176</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44522</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44991</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45566</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45540</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45386</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45161</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44614</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44636</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45180</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45528</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44859</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45777</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45280</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45350</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45252</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>44495</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44852</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44883</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45327</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45414</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45790</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45924</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45790</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45790</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45926</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44616</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45014</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44588</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>44838</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45226</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45610</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45244</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45798</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45797</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45798</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>45798</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45798</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44524</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45114</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45702</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45328</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45555</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44897</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45209</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44986</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44778</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>45089</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45448</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45684</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45553</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45946</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>45817</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>44634</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44911</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45581</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44761</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45189</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45636</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45209</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44614</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44676</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45454</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>45830</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45740</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44722</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44722</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45230</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45012</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45057</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45169</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45713</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44733</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44907</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45597</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45632</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45702</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45315</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45974</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45729</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44887</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45378</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45163</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45225</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45225</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>44899</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>45250</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45713</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45321</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45228</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45309</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44522</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>44868</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45211</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45048</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45671</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45007</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45345</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45082</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44909</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44624</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>44624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45411</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44970</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>44896</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45041</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45531</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44979</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45068</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44859</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45501</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46108</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46112</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46113</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44848</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45993</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45994</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45993</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44566</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46125</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46129</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46132</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46121</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46121</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46121</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46132</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44855</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45805</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45140</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45895</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>44807</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45482</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45213</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44914</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45869</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45888</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46036</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45974</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45718</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44785</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>44648</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>44979</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45056</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46044</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44739</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44769</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>45036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46056</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46044</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45993</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46071</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>46071</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>46077</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>46079</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>46079</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46079</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46082</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46080</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>46080</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>46080</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>46083</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>46168</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>46168</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46168</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>46168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46168</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46121</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45618</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46170</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45932</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>46175</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>46176</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>46181</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>46170</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>46188</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>46188</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>46196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>46266</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>46265</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>46267</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>46267</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46267</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>46229</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>46273</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46240</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>46244</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>46091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>46283</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>46286</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46249</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>46175</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>46250</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>46251</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46251</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46251</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>46253</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>46295</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>46205</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>46296</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>46258</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>46258</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>46126</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>46252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44588</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44685</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44964</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45686</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44742</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45446</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45403</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46164</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>45713</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>46175</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>45323</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2297,7 +2297,7 @@
         <v>44624</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45666</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2644,7 +2644,7 @@
         <v>45039</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46108</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>45002</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3104,7 +3104,7 @@
         <v>46037</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46079</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45209</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44956</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>45518</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45839</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45600</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4224,7 +4224,7 @@
         <v>46097</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45714</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45518</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>45212</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4776,7 +4776,7 @@
         <v>44986</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45777</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5105,7 +5105,7 @@
         <v>46044</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46079</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44724</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44578</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5554,7 +5554,7 @@
         <v>45272</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5661,7 +5661,7 @@
         <v>44771</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>45666</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5880,7 +5880,7 @@
         <v>44790</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>45789</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6103,7 +6103,7 @@
         <v>45142</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>46071</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6326,7 +6326,7 @@
         <v>46071</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6437,7 +6437,7 @@
         <v>46071</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6544,7 +6544,7 @@
         <v>45965</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
         <v>46205</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44971</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>44986</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7848,7 +7848,7 @@
         <v>45068</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>45211</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>45166</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8171,7 +8171,7 @@
         <v>45798</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>44826</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45838</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8494,7 +8494,7 @@
         <v>44907</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>44798</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>44848</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8817,7 +8817,7 @@
         <v>44624</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8923,7 +8923,7 @@
         <v>44596</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9029,7 +9029,7 @@
         <v>45219</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44785</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>46044</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9356,7 +9356,7 @@
         <v>46068</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>46155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>46258</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44697</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44503</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44735</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10104,7 +10104,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10209,7 +10209,7 @@
         <v>44608</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>44911</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10429,7 +10429,7 @@
         <v>45140</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>45740</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10644,7 +10644,7 @@
         <v>45643</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10749,7 +10749,7 @@
         <v>45211</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10854,7 +10854,7 @@
         <v>45540</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10959,7 +10959,7 @@
         <v>45350</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11064,7 +11064,7 @@
         <v>44495</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11174,7 +11174,7 @@
         <v>45182</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11279,7 +11279,7 @@
         <v>44881</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>45348</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45377</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45156</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44624</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11809,7 +11809,7 @@
         <v>45007</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11919,7 +11919,7 @@
         <v>45196</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45624</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45740</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45931</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45191</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12459,7 +12459,7 @@
         <v>44572</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>44637</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>45740</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12789,7 +12789,7 @@
         <v>45954</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12899,7 +12899,7 @@
         <v>45163</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13004,7 +13004,7 @@
         <v>44785</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13109,7 +13109,7 @@
         <v>44774</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13214,7 +13214,7 @@
         <v>44854</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13319,7 +13319,7 @@
         <v>45510</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13424,7 +13424,7 @@
         <v>45343</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13529,7 +13529,7 @@
         <v>44503</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>44953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13954,7 +13954,7 @@
         <v>44637</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>45586</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14168,7 +14168,7 @@
         <v>46035</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14278,7 +14278,7 @@
         <v>46035</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14392,7 +14392,7 @@
         <v>44518</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45105</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45141</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14712,7 +14712,7 @@
         <v>46056</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14817,7 +14817,7 @@
         <v>46071</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
         <v>46079</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15037,7 +15037,7 @@
         <v>46168</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>46181</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>46181</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>46209</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>46294</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44722</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15910,7 +15910,7 @@
         <v>44614</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15983,7 +15983,7 @@
         <v>44535</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44869</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44752</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44769</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44745</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44879</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44643</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44739</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17093,7 +17093,7 @@
         <v>44636</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17166,7 +17166,7 @@
         <v>44578</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44778</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44769</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44752</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44752</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44770</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>44769</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17760,7 +17760,7 @@
         <v>44769</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17833,7 +17833,7 @@
         <v>44846</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>44566</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17989,7 +17989,7 @@
         <v>44640</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>44839</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18135,7 +18135,7 @@
         <v>44886</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44830</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>44725</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18354,7 +18354,7 @@
         <v>44862</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18427,7 +18427,7 @@
         <v>44854</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44610</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18578,7 +18578,7 @@
         <v>44643</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>45225</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44697</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44636</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44705</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44818</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45222</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>44872</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>45330</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45720</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>44864</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45216</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>45250</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>45555</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>45250</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19688,7 +19688,7 @@
         <v>45230</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19761,7 +19761,7 @@
         <v>45311</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>45358</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45740</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>44741</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>45228</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45260</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45398</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45271</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45239</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20428,7 +20428,7 @@
         <v>45103</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20501,7 +20501,7 @@
         <v>45441</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20574,7 +20574,7 @@
         <v>45244</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>44862</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>44701</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44796</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45022</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45270</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21017,7 +21017,7 @@
         <v>45034</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21090,7 +21090,7 @@
         <v>45114</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21163,7 +21163,7 @@
         <v>45104</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45257</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21309,7 +21309,7 @@
         <v>45161</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21382,7 +21382,7 @@
         <v>45518</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45574</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45119</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45081</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45081</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45001</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21830,7 +21830,7 @@
         <v>44887</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21903,7 +21903,7 @@
         <v>45365</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45299</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22049,7 +22049,7 @@
         <v>45299</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22122,7 +22122,7 @@
         <v>45022</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22195,7 +22195,7 @@
         <v>45147</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22268,7 +22268,7 @@
         <v>44517</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22341,7 +22341,7 @@
         <v>45110</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22414,7 +22414,7 @@
         <v>45149</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22492,7 +22492,7 @@
         <v>45322</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22565,7 +22565,7 @@
         <v>45555</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22638,7 +22638,7 @@
         <v>44553</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22711,7 +22711,7 @@
         <v>45331</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22784,7 +22784,7 @@
         <v>45256</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>45140</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>44931</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>44909</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44580</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>45217</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23242,7 +23242,7 @@
         <v>45250</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23320,7 +23320,7 @@
         <v>45161</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23393,7 +23393,7 @@
         <v>45066</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23466,7 +23466,7 @@
         <v>45163</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23539,7 +23539,7 @@
         <v>44907</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23612,7 +23612,7 @@
         <v>44980</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23685,7 +23685,7 @@
         <v>44887</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45667</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45478</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23904,7 +23904,7 @@
         <v>45230</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23977,7 +23977,7 @@
         <v>45230</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24050,7 +24050,7 @@
         <v>45013</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24123,7 +24123,7 @@
         <v>45632</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24196,7 +24196,7 @@
         <v>45176</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44522</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44991</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45566</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45540</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24561,7 +24561,7 @@
         <v>45244</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45386</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45161</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24785,7 +24785,7 @@
         <v>44957</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24858,7 +24858,7 @@
         <v>44614</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24931,7 +24931,7 @@
         <v>44636</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25004,7 +25004,7 @@
         <v>45180</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25077,7 +25077,7 @@
         <v>45528</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25150,7 +25150,7 @@
         <v>44859</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25228,7 +25228,7 @@
         <v>45777</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>45280</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25379,7 +25379,7 @@
         <v>44544</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25452,7 +25452,7 @@
         <v>45175</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25525,7 +25525,7 @@
         <v>45163</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25598,7 +25598,7 @@
         <v>45350</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25671,7 +25671,7 @@
         <v>45252</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25744,7 +25744,7 @@
         <v>44495</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45008</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25890,7 +25890,7 @@
         <v>44852</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44883</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26036,7 +26036,7 @@
         <v>45327</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45414</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26182,7 +26182,7 @@
         <v>45161</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26255,7 +26255,7 @@
         <v>44896</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26333,7 +26333,7 @@
         <v>45790</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45924</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26484,7 +26484,7 @@
         <v>45790</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26557,7 +26557,7 @@
         <v>45790</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26630,7 +26630,7 @@
         <v>45926</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26708,7 +26708,7 @@
         <v>44616</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26781,7 +26781,7 @@
         <v>45014</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26859,7 +26859,7 @@
         <v>44588</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26932,7 +26932,7 @@
         <v>44838</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27005,7 +27005,7 @@
         <v>44958</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>45226</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27156,7 +27156,7 @@
         <v>45555</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27229,7 +27229,7 @@
         <v>45610</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27302,7 +27302,7 @@
         <v>45244</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27375,7 +27375,7 @@
         <v>45166</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27448,7 +27448,7 @@
         <v>44979</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27521,7 +27521,7 @@
         <v>44610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27594,7 +27594,7 @@
         <v>45932</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45798</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45797</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27823,7 +27823,7 @@
         <v>45798</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44602</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27969,7 +27969,7 @@
         <v>45798</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45798</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44524</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45114</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>45702</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28334,7 +28334,7 @@
         <v>45328</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28407,7 +28407,7 @@
         <v>45555</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28480,7 +28480,7 @@
         <v>44897</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28558,7 +28558,7 @@
         <v>45209</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28631,7 +28631,7 @@
         <v>45166</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28704,7 +28704,7 @@
         <v>44986</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28777,7 +28777,7 @@
         <v>44988</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28855,7 +28855,7 @@
         <v>44778</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28928,7 +28928,7 @@
         <v>45089</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29001,7 +29001,7 @@
         <v>45448</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44531</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29147,7 +29147,7 @@
         <v>45684</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29220,7 +29220,7 @@
         <v>45553</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29293,7 +29293,7 @@
         <v>45946</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>45817</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29444,7 +29444,7 @@
         <v>44634</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29517,7 +29517,7 @@
         <v>44911</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29595,7 +29595,7 @@
         <v>45581</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>44761</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29741,7 +29741,7 @@
         <v>45189</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29819,7 +29819,7 @@
         <v>45636</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>45209</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -29965,7 +29965,7 @@
         <v>44614</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44676</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30111,7 +30111,7 @@
         <v>45454</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30184,7 +30184,7 @@
         <v>44970</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30257,7 +30257,7 @@
         <v>45830</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30330,7 +30330,7 @@
         <v>45830</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45740</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30481,7 +30481,7 @@
         <v>44722</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30554,7 +30554,7 @@
         <v>44722</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30627,7 +30627,7 @@
         <v>45230</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>44846</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30778,7 +30778,7 @@
         <v>44819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30851,7 +30851,7 @@
         <v>45012</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30929,7 +30929,7 @@
         <v>45964</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31002,7 +31002,7 @@
         <v>45964</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31075,7 +31075,7 @@
         <v>45057</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31148,7 +31148,7 @@
         <v>45169</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31221,7 +31221,7 @@
         <v>45713</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31294,7 +31294,7 @@
         <v>44733</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31367,7 +31367,7 @@
         <v>44907</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45597</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45632</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45702</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45315</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45974</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45729</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>44887</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -31951,7 +31951,7 @@
         <v>45378</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45163</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32102,7 +32102,7 @@
         <v>45225</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32175,7 +32175,7 @@
         <v>45225</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>44899</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32321,7 +32321,7 @@
         <v>45250</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32394,7 +32394,7 @@
         <v>45030</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32467,7 +32467,7 @@
         <v>45713</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32540,7 +32540,7 @@
         <v>45321</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32613,7 +32613,7 @@
         <v>44900</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45228</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32759,7 +32759,7 @@
         <v>45309</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32832,7 +32832,7 @@
         <v>44522</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -32910,7 +32910,7 @@
         <v>44958</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -32983,7 +32983,7 @@
         <v>44868</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45880</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33134,7 +33134,7 @@
         <v>45211</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33207,7 +33207,7 @@
         <v>45048</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33280,7 +33280,7 @@
         <v>45671</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45007</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33426,7 +33426,7 @@
         <v>45345</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33499,7 +33499,7 @@
         <v>45082</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33572,7 +33572,7 @@
         <v>44909</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33650,7 +33650,7 @@
         <v>44624</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33723,7 +33723,7 @@
         <v>44624</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33796,7 +33796,7 @@
         <v>45411</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>44970</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>44896</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34025,7 +34025,7 @@
         <v>45041</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34098,7 +34098,7 @@
         <v>45244</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34176,7 +34176,7 @@
         <v>45531</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34249,7 +34249,7 @@
         <v>44979</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>45068</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44859</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34478,7 +34478,7 @@
         <v>45501</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34551,7 +34551,7 @@
         <v>46108</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>46112</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46113</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>44848</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45993</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45994</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35004,7 +35004,7 @@
         <v>45994</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35082,7 +35082,7 @@
         <v>45993</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45993</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35228,7 +35228,7 @@
         <v>44566</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35301,7 +35301,7 @@
         <v>46125</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35379,7 +35379,7 @@
         <v>45995</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35457,7 +35457,7 @@
         <v>46126</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35530,7 +35530,7 @@
         <v>45995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35603,7 +35603,7 @@
         <v>46000</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35681,7 +35681,7 @@
         <v>46126</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35754,7 +35754,7 @@
         <v>46129</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>46132</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>44960</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -35978,7 +35978,7 @@
         <v>46121</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36051,7 +36051,7 @@
         <v>46121</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36124,7 +36124,7 @@
         <v>46121</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36197,7 +36197,7 @@
         <v>46132</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36275,7 +36275,7 @@
         <v>44855</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36348,7 +36348,7 @@
         <v>44855</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36421,7 +36421,7 @@
         <v>45805</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>45140</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36567,7 +36567,7 @@
         <v>45895</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36640,7 +36640,7 @@
         <v>45072</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36713,7 +36713,7 @@
         <v>44807</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36786,7 +36786,7 @@
         <v>45482</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36859,7 +36859,7 @@
         <v>45213</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -36937,7 +36937,7 @@
         <v>45510</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37010,7 +37010,7 @@
         <v>44914</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37083,7 +37083,7 @@
         <v>45869</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37156,7 +37156,7 @@
         <v>45888</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37229,7 +37229,7 @@
         <v>46036</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37307,7 +37307,7 @@
         <v>45974</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>45718</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44785</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>44648</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>44979</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37672,7 +37672,7 @@
         <v>45056</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37745,7 +37745,7 @@
         <v>46044</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37818,7 +37818,7 @@
         <v>44739</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37891,7 +37891,7 @@
         <v>44769</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -37964,7 +37964,7 @@
         <v>45791</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38037,7 +38037,7 @@
         <v>45036</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>46056</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38183,7 +38183,7 @@
         <v>46044</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45993</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38334,7 +38334,7 @@
         <v>46071</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>46071</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38480,7 +38480,7 @@
         <v>46077</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38553,7 +38553,7 @@
         <v>46079</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>46079</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>46079</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>46082</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38860,7 +38860,7 @@
         <v>46080</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -38938,7 +38938,7 @@
         <v>46080</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39016,7 +39016,7 @@
         <v>46080</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>46083</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39172,7 +39172,7 @@
         <v>45224</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39250,7 +39250,7 @@
         <v>46168</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39323,7 +39323,7 @@
         <v>46168</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39401,7 +39401,7 @@
         <v>46168</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39474,7 +39474,7 @@
         <v>46168</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39552,7 +39552,7 @@
         <v>46168</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>46168</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39708,7 +39708,7 @@
         <v>46121</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>45618</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39854,7 +39854,7 @@
         <v>46170</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>45932</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40025,7 +40025,7 @@
         <v>46175</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40098,7 +40098,7 @@
         <v>46176</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40176,7 +40176,7 @@
         <v>46181</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>46181</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40322,7 +40322,7 @@
         <v>46181</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>46183</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40478,7 +40478,7 @@
         <v>46170</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40556,7 +40556,7 @@
         <v>46188</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40629,7 +40629,7 @@
         <v>46188</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40702,7 +40702,7 @@
         <v>46188</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40775,7 +40775,7 @@
         <v>46196</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40848,7 +40848,7 @@
         <v>46266</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>46265</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -40999,7 +40999,7 @@
         <v>46267</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>46267</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41155,7 +41155,7 @@
         <v>46267</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41233,7 +41233,7 @@
         <v>46229</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41306,7 +41306,7 @@
         <v>46273</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>46273</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41462,7 +41462,7 @@
         <v>46273</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41540,7 +41540,7 @@
         <v>46240</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>46244</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41686,7 +41686,7 @@
         <v>46091</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41759,7 +41759,7 @@
         <v>46283</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41832,7 +41832,7 @@
         <v>46286</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>46249</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>46175</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42051,7 +42051,7 @@
         <v>46250</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42124,7 +42124,7 @@
         <v>46293</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42202,7 +42202,7 @@
         <v>46251</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46251</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46251</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42436,7 +42436,7 @@
         <v>46253</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42509,7 +42509,7 @@
         <v>46295</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>46205</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42655,7 +42655,7 @@
         <v>46296</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>46258</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42806,7 +42806,7 @@
         <v>46258</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42884,7 +42884,7 @@
         <v>46258</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>46126</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>46252</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>46252</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>46185</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44588</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43327,7 +43327,7 @@
         <v>44685</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44964</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43483,7 +43483,7 @@
         <v>45686</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>44742</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45446</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45403</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46164</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45039</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44956</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44814</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45600</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45714</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45212</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45518</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>44986</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44724</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45789</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>44578</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44790</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45142</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44826</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44971</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45838</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44907</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45166</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44785</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45798</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44697</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44503</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45140</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44785</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44881</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45540</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44774</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45740</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45348</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45343</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45141</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44518</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45954</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45740</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45156</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46168</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>46181</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45586</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44624</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46056</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>46071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44637</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>46209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44865</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45350</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45377</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44854</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46294</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45196</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44614</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44722</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44869</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44752</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44745</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44769</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44879</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44770</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44769</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44640</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44725</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44778</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44769</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>44839</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44886</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44854</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44697</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>44769</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44846</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>44636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44752</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44752</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>44566</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44610</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44643</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44818</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44705</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44980</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44868</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45531</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45378</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44495</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45636</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45068</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44544</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45510</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45482</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45597</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45225</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45226</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45166</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45270</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44970</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45309</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44733</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45209</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44522</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>44931</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44859</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45311</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44872</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45299</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44859</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45228</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45057</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45034</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44602</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45244</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45398</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45667</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45089</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>44624</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45566</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44838</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45581</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45740</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45358</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44722</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44722</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44785</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44616</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45553</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45103</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45869</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44807</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45791</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45213</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45322</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45280</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>44862</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44524</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44522</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45411</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45924</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45555</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45926</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45932</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45081</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45081</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45228</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45022</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45632</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45022</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44897</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44778</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45331</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45066</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45330</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44864</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>44855</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45250</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45250</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>44855</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45224</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45528</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44896</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44970</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45140</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45713</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>44957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45244</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44991</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>46168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45994</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>46168</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45995</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45056</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>46168</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45230</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>46168</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>46168</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>46000</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45119</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>46121</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>46170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>44566</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>44624</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45618</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45041</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45222</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45166</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45932</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>44701</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>44909</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45518</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45271</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>46175</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45632</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>46176</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45321</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>46181</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46036</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44676</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46044</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45013</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45230</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45230</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>46170</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>46044</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>46183</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>46071</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>46071</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45163</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44636</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>46077</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46080</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>46080</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>46079</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>46188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46079</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>46079</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>46080</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>46083</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44887</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45114</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46196</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45161</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45012</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46108</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44887</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46112</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44958</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46113</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44907</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44900</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45072</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45114</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46125</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45299</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>46126</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>46121</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>46121</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46129</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46121</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45082</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>46132</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45030</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>46132</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>44887</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45169</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45225</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45501</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45888</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45555</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45805</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45718</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45161</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45250</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45211</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45225</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44848</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45441</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>44614</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45720</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45540</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>44614</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>46273</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46229</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46273</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45327</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>44553</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45345</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44648</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44739</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45454</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45478</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46283</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45713</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44580</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45140</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44819</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46286</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>44769</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45110</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45250</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>46244</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45161</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>44960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45244</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45328</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45175</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45036</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>44907</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45365</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44634</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45176</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>46251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45180</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46251</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46251</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45256</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45007</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45448</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46205</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45386</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>44610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45014</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>46295</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45671</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45163</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>44958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>46258</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45777</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>46258</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>46258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>46296</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45414</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45252</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44883</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44852</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45008</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45790</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45790</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45790</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46252</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45610</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45555</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45797</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45798</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>46307</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45702</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>46252</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45798</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45798</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>46249</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46266</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46265</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45684</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45817</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>46267</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46267</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45830</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45830</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45702</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45729</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44899</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44964</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45686</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44742</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44588</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>44685</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45446</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45403</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46164</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44481</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>44998</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2063,7 +2063,7 @@
         <v>44650</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2293,7 +2293,7 @@
         <v>45323</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>44495</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2528,7 +2528,7 @@
         <v>45039</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2639,7 +2639,7 @@
         <v>45666</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>44078</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>45002</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2985,7 +2985,7 @@
         <v>46037</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46079</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>46108</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3329,7 +3329,7 @@
         <v>46147</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>45518</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>44533</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>45209</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>44956</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3884,7 +3884,7 @@
         <v>46097</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3993,7 +3993,7 @@
         <v>44814</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>45839</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45600</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4333,7 +4333,7 @@
         <v>45714</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4447,7 +4447,7 @@
         <v>44596</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4555,7 +4555,7 @@
         <v>45212</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4668,7 +4668,7 @@
         <v>46044</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4781,7 +4781,7 @@
         <v>45518</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4889,7 +4889,7 @@
         <v>46112</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4997,7 +4997,7 @@
         <v>46079</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5110,7 +5110,7 @@
         <v>44986</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>45777</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44724</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5438,7 +5438,7 @@
         <v>44771</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5545,7 +5545,7 @@
         <v>45789</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5652,7 +5652,7 @@
         <v>45965</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5973,7 +5973,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6084,7 +6084,7 @@
         <v>44578</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6200,7 +6200,7 @@
         <v>45272</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6307,7 +6307,7 @@
         <v>46205</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44790</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6642,7 +6642,7 @@
         <v>45142</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>45275</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6874,7 +6874,7 @@
         <v>44830</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6981,7 +6981,7 @@
         <v>45530</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7088,7 +7088,7 @@
         <v>44637</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44624</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7304,7 +7304,7 @@
         <v>44715</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7415,7 +7415,7 @@
         <v>44826</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7521,7 +7521,7 @@
         <v>45219</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>44865</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7746,7 +7746,7 @@
         <v>45400</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44798</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7958,7 +7958,7 @@
         <v>44971</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8064,7 +8064,7 @@
         <v>45838</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>46068</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8387,7 +8387,7 @@
         <v>45211</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8493,7 +8493,7 @@
         <v>45068</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8599,7 +8599,7 @@
         <v>44907</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44596</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45166</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44848</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9033,7 +9033,7 @@
         <v>44785</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>46155</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44624</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>44986</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9457,7 +9457,7 @@
         <v>46258</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>45798</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>44697</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9789,7 +9789,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9894,7 +9894,7 @@
         <v>44503</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44608</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10109,7 +10109,7 @@
         <v>44838</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10214,7 +10214,7 @@
         <v>44735</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10319,7 +10319,7 @@
         <v>45140</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45510</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44785</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10634,7 +10634,7 @@
         <v>44881</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45007</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>45540</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44774</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11059,7 +11059,7 @@
         <v>45740</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45348</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11274,7 +11274,7 @@
         <v>45343</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11379,7 +11379,7 @@
         <v>45931</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11489,7 +11489,7 @@
         <v>45182</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11594,7 +11594,7 @@
         <v>45141</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44518</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11804,7 +11804,7 @@
         <v>45954</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44572</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12024,7 +12024,7 @@
         <v>45740</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45156</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45643</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12349,7 +12349,7 @@
         <v>45222</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12454,7 +12454,7 @@
         <v>46168</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12788,7 +12788,7 @@
         <v>46181</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>45586</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13002,7 +13002,7 @@
         <v>46181</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44624</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13217,7 +13217,7 @@
         <v>46056</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13322,7 +13322,7 @@
         <v>46071</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13432,7 +13432,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13537,7 +13537,7 @@
         <v>46079</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44637</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>44911</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>44953</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44637</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45105</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14191,7 +14191,7 @@
         <v>46209</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14411,7 +14411,7 @@
         <v>44865</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>45350</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45377</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14731,7 +14731,7 @@
         <v>44854</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14836,7 +14836,7 @@
         <v>44503</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15051,7 +15051,7 @@
         <v>45211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15156,7 +15156,7 @@
         <v>45191</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>46294</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15366,7 +15366,7 @@
         <v>45196</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45624</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15581,7 +15581,7 @@
         <v>46149</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15686,7 +15686,7 @@
         <v>44501</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>44536</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15832,7 +15832,7 @@
         <v>44614</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15905,7 +15905,7 @@
         <v>44535</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44722</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16056,7 +16056,7 @@
         <v>44869</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16134,7 +16134,7 @@
         <v>44608</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16212,7 +16212,7 @@
         <v>44752</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
         <v>44720</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16363,7 +16363,7 @@
         <v>44873</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16436,7 +16436,7 @@
         <v>44745</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44769</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>44839</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16655,7 +16655,7 @@
         <v>44579</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>44807</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16801,7 +16801,7 @@
         <v>44855</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16874,7 +16874,7 @@
         <v>44879</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>44739</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17020,7 +17020,7 @@
         <v>44770</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17098,7 +17098,7 @@
         <v>44769</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>44640</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17244,7 +17244,7 @@
         <v>44725</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17317,7 +17317,7 @@
         <v>44830</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>44643</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17463,7 +17463,7 @@
         <v>44778</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17536,7 +17536,7 @@
         <v>44588</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17609,7 +17609,7 @@
         <v>44769</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17682,7 +17682,7 @@
         <v>44839</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17755,7 +17755,7 @@
         <v>44886</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>44854</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17901,7 +17901,7 @@
         <v>44697</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -17974,7 +17974,7 @@
         <v>44578</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>44769</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18125,7 +18125,7 @@
         <v>44846</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18203,7 +18203,7 @@
         <v>44636</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18276,7 +18276,7 @@
         <v>44752</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18349,7 +18349,7 @@
         <v>44752</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>44566</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>44862</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18573,7 +18573,7 @@
         <v>44610</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18651,7 +18651,7 @@
         <v>44643</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18724,7 +18724,7 @@
         <v>44636</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18797,7 +18797,7 @@
         <v>44818</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18870,7 +18870,7 @@
         <v>44705</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -18943,7 +18943,7 @@
         <v>44980</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>44868</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45531</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45555</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45378</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>44531</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19391,7 +19391,7 @@
         <v>44517</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19464,7 +19464,7 @@
         <v>44986</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19537,7 +19537,7 @@
         <v>44914</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19610,7 +19610,7 @@
         <v>44495</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19683,7 +19683,7 @@
         <v>45636</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19756,7 +19756,7 @@
         <v>45068</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19834,7 +19834,7 @@
         <v>44544</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19907,7 +19907,7 @@
         <v>45510</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>45239</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20058,7 +20058,7 @@
         <v>44796</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20131,7 +20131,7 @@
         <v>45482</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20204,7 +20204,7 @@
         <v>45597</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20277,7 +20277,7 @@
         <v>45225</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20350,7 +20350,7 @@
         <v>45226</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20423,7 +20423,7 @@
         <v>45166</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20496,7 +20496,7 @@
         <v>45270</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20569,7 +20569,7 @@
         <v>44970</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45149</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>45309</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44733</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45209</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>44522</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>44931</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21100,7 +21100,7 @@
         <v>44979</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45147</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44859</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45311</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>44588</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>44872</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45299</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>44896</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>44859</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45228</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21845,7 +21845,7 @@
         <v>45057</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>45034</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -21991,7 +21991,7 @@
         <v>44602</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22064,7 +22064,7 @@
         <v>45244</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22137,7 +22137,7 @@
         <v>45398</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45667</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22283,7 +22283,7 @@
         <v>45089</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22356,7 +22356,7 @@
         <v>44624</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45566</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22502,7 +22502,7 @@
         <v>45260</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22575,7 +22575,7 @@
         <v>44838</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22648,7 +22648,7 @@
         <v>44761</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45581</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22794,7 +22794,7 @@
         <v>45163</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22867,7 +22867,7 @@
         <v>45740</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -22945,7 +22945,7 @@
         <v>45358</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>45974</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23091,7 +23091,7 @@
         <v>44722</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23164,7 +23164,7 @@
         <v>44722</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>44785</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23310,7 +23310,7 @@
         <v>44616</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>45553</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45103</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23602,7 +23602,7 @@
         <v>45869</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>44807</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23748,7 +23748,7 @@
         <v>45791</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23821,7 +23821,7 @@
         <v>45993</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23894,7 +23894,7 @@
         <v>45213</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -23972,7 +23972,7 @@
         <v>45104</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45322</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24118,7 +24118,7 @@
         <v>45280</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24191,7 +24191,7 @@
         <v>44862</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24269,7 +24269,7 @@
         <v>44524</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24342,7 +24342,7 @@
         <v>44522</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24415,7 +24415,7 @@
         <v>45411</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24488,7 +24488,7 @@
         <v>45924</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24566,7 +24566,7 @@
         <v>44979</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24639,7 +24639,7 @@
         <v>45555</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24712,7 +24712,7 @@
         <v>45926</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24790,7 +24790,7 @@
         <v>45932</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24868,7 +24868,7 @@
         <v>45081</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45081</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25014,7 +25014,7 @@
         <v>44988</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25092,7 +25092,7 @@
         <v>45228</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25165,7 +25165,7 @@
         <v>45022</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25238,7 +25238,7 @@
         <v>45632</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25311,7 +25311,7 @@
         <v>45022</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>44897</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25462,7 +25462,7 @@
         <v>44778</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25535,7 +25535,7 @@
         <v>45946</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45331</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45066</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>44979</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45330</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44864</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -25978,7 +25978,7 @@
         <v>44855</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26051,7 +26051,7 @@
         <v>45250</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26129,7 +26129,7 @@
         <v>45250</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>44855</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>45224</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26353,7 +26353,7 @@
         <v>45964</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26426,7 +26426,7 @@
         <v>45964</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26499,7 +26499,7 @@
         <v>45528</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26572,7 +26572,7 @@
         <v>44896</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45974</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44970</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26796,7 +26796,7 @@
         <v>45140</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26869,7 +26869,7 @@
         <v>45713</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -26942,7 +26942,7 @@
         <v>44957</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27015,7 +27015,7 @@
         <v>45209</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27088,7 +27088,7 @@
         <v>45244</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27166,7 +27166,7 @@
         <v>45993</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27239,7 +27239,7 @@
         <v>45993</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27312,7 +27312,7 @@
         <v>44991</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27385,7 +27385,7 @@
         <v>45993</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>46168</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27536,7 +27536,7 @@
         <v>45994</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>46168</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27692,7 +27692,7 @@
         <v>45995</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45995</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27843,7 +27843,7 @@
         <v>45994</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -27921,7 +27921,7 @@
         <v>45048</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -27994,7 +27994,7 @@
         <v>46168</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28067,7 +28067,7 @@
         <v>45056</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28140,7 +28140,7 @@
         <v>46168</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28218,7 +28218,7 @@
         <v>45574</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28296,7 +28296,7 @@
         <v>45230</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28369,7 +28369,7 @@
         <v>46168</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28442,7 +28442,7 @@
         <v>46168</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28520,7 +28520,7 @@
         <v>46000</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45119</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28671,7 +28671,7 @@
         <v>46121</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28744,7 +28744,7 @@
         <v>46170</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28842,7 +28842,7 @@
         <v>44566</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28915,7 +28915,7 @@
         <v>44624</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -28988,7 +28988,7 @@
         <v>45618</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29061,7 +29061,7 @@
         <v>45041</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29134,7 +29134,7 @@
         <v>45222</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29207,7 +29207,7 @@
         <v>45166</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45932</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>44701</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>45740</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29504,7 +29504,7 @@
         <v>44909</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>45518</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45271</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29728,7 +29728,7 @@
         <v>46175</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29801,7 +29801,7 @@
         <v>45257</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45632</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>46176</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30025,7 +30025,7 @@
         <v>45315</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30098,7 +30098,7 @@
         <v>45321</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30171,7 +30171,7 @@
         <v>46181</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>46181</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30317,7 +30317,7 @@
         <v>46036</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44676</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30468,7 +30468,7 @@
         <v>46044</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30541,7 +30541,7 @@
         <v>46181</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30619,7 +30619,7 @@
         <v>45013</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30692,7 +30692,7 @@
         <v>45230</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45230</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30838,7 +30838,7 @@
         <v>46056</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -30911,7 +30911,7 @@
         <v>46170</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>46044</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>46183</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31145,7 +31145,7 @@
         <v>46188</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>46071</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31291,7 +31291,7 @@
         <v>46071</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45163</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31437,7 +31437,7 @@
         <v>44741</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31510,7 +31510,7 @@
         <v>44636</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31583,7 +31583,7 @@
         <v>46077</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>46188</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31729,7 +31729,7 @@
         <v>46080</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31807,7 +31807,7 @@
         <v>46080</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31885,7 +31885,7 @@
         <v>46079</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>46188</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>46079</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32114,7 +32114,7 @@
         <v>46079</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>46080</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32270,7 +32270,7 @@
         <v>46082</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32343,7 +32343,7 @@
         <v>46083</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32421,7 +32421,7 @@
         <v>44887</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32494,7 +32494,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32567,7 +32567,7 @@
         <v>44911</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32645,7 +32645,7 @@
         <v>45114</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32718,7 +32718,7 @@
         <v>46196</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32791,7 +32791,7 @@
         <v>45161</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32864,7 +32864,7 @@
         <v>45012</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>46108</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33020,7 +33020,7 @@
         <v>44887</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33093,7 +33093,7 @@
         <v>46112</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33166,7 +33166,7 @@
         <v>44958</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>46113</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33312,7 +33312,7 @@
         <v>44907</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33385,7 +33385,7 @@
         <v>44900</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33458,7 +33458,7 @@
         <v>45072</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33531,7 +33531,7 @@
         <v>45217</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33609,7 +33609,7 @@
         <v>45114</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33682,7 +33682,7 @@
         <v>46126</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>46125</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45299</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33906,7 +33906,7 @@
         <v>46126</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -33979,7 +33979,7 @@
         <v>46121</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34052,7 +34052,7 @@
         <v>46121</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34125,7 +34125,7 @@
         <v>46129</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>46121</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34271,7 +34271,7 @@
         <v>45189</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34349,7 +34349,7 @@
         <v>45082</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34422,7 +34422,7 @@
         <v>46132</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34500,7 +34500,7 @@
         <v>45030</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34573,7 +34573,7 @@
         <v>46132</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>44887</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34724,7 +34724,7 @@
         <v>45169</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34797,7 +34797,7 @@
         <v>45225</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34870,7 +34870,7 @@
         <v>45501</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45888</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35016,7 +35016,7 @@
         <v>45555</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35089,7 +35089,7 @@
         <v>45805</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35162,7 +35162,7 @@
         <v>45718</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35235,7 +35235,7 @@
         <v>44846</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45161</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35386,7 +35386,7 @@
         <v>45250</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35464,7 +35464,7 @@
         <v>45211</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45225</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35610,7 +35610,7 @@
         <v>44848</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35688,7 +35688,7 @@
         <v>45441</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>44614</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35834,7 +35834,7 @@
         <v>45720</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35907,7 +35907,7 @@
         <v>45230</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -35980,7 +35980,7 @@
         <v>46273</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36058,7 +36058,7 @@
         <v>45540</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36131,7 +36131,7 @@
         <v>44614</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36204,7 +36204,7 @@
         <v>46273</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36282,7 +36282,7 @@
         <v>46229</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>46273</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36433,7 +36433,7 @@
         <v>44909</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36511,7 +36511,7 @@
         <v>45327</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45001</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36662,7 +36662,7 @@
         <v>44553</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45345</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36808,7 +36808,7 @@
         <v>44648</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36881,7 +36881,7 @@
         <v>46240</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -36954,7 +36954,7 @@
         <v>44739</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37027,7 +37027,7 @@
         <v>45454</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37100,7 +37100,7 @@
         <v>45478</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37173,7 +37173,7 @@
         <v>46283</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37246,7 +37246,7 @@
         <v>45713</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>44580</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37392,7 +37392,7 @@
         <v>46091</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37465,7 +37465,7 @@
         <v>45140</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37543,7 +37543,7 @@
         <v>44819</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37616,7 +37616,7 @@
         <v>46286</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37689,7 +37689,7 @@
         <v>44769</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37762,7 +37762,7 @@
         <v>45110</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45250</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>46244</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -37981,7 +37981,7 @@
         <v>45161</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38054,7 +38054,7 @@
         <v>44960</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38127,7 +38127,7 @@
         <v>45244</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38205,7 +38205,7 @@
         <v>45328</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45175</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45036</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38424,7 +38424,7 @@
         <v>44907</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45365</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38570,7 +38570,7 @@
         <v>45244</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38643,7 +38643,7 @@
         <v>46250</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38716,7 +38716,7 @@
         <v>46175</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>46293</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38867,7 +38867,7 @@
         <v>44634</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45176</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39013,7 +39013,7 @@
         <v>45216</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>46251</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39169,7 +39169,7 @@
         <v>46253</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39242,7 +39242,7 @@
         <v>45180</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>46251</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39393,7 +39393,7 @@
         <v>46251</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39471,7 +39471,7 @@
         <v>45256</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39544,7 +39544,7 @@
         <v>45007</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45448</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39690,7 +39690,7 @@
         <v>46205</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39763,7 +39763,7 @@
         <v>45386</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39836,7 +39836,7 @@
         <v>44610</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39909,7 +39909,7 @@
         <v>45014</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -39987,7 +39987,7 @@
         <v>46295</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45671</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40133,7 +40133,7 @@
         <v>45163</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40206,7 +40206,7 @@
         <v>44958</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40284,7 +40284,7 @@
         <v>46258</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40362,7 +40362,7 @@
         <v>45777</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>46258</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40518,7 +40518,7 @@
         <v>46258</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40596,7 +40596,7 @@
         <v>46296</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40669,7 +40669,7 @@
         <v>45414</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45252</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40815,7 +40815,7 @@
         <v>45350</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44883</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44852</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41034,7 +41034,7 @@
         <v>45008</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41107,7 +41107,7 @@
         <v>45790</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41180,7 +41180,7 @@
         <v>45790</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45790</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41326,7 +41326,7 @@
         <v>46252</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45610</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41472,7 +41472,7 @@
         <v>45555</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45797</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41618,7 +41618,7 @@
         <v>45798</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41691,7 +41691,7 @@
         <v>45798</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41764,7 +41764,7 @@
         <v>46307</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41837,7 +41837,7 @@
         <v>45702</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41910,7 +41910,7 @@
         <v>46252</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -41983,7 +41983,7 @@
         <v>45798</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42056,7 +42056,7 @@
         <v>45798</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42134,7 +42134,7 @@
         <v>46185</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>46249</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42280,7 +42280,7 @@
         <v>46266</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42358,7 +42358,7 @@
         <v>46265</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42431,7 +42431,7 @@
         <v>45684</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>46267</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42582,7 +42582,7 @@
         <v>45817</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42660,7 +42660,7 @@
         <v>46267</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42738,7 +42738,7 @@
         <v>46267</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42816,7 +42816,7 @@
         <v>45830</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45830</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -42962,7 +42962,7 @@
         <v>45702</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43035,7 +43035,7 @@
         <v>45729</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43108,7 +43108,7 @@
         <v>44899</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43181,7 +43181,7 @@
         <v>45880</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43254,7 +43254,7 @@
         <v>44964</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43332,7 +43332,7 @@
         <v>45686</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43405,7 +43405,7 @@
         <v>44742</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43478,7 +43478,7 @@
         <v>44588</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43551,7 +43551,7 @@
         <v>44685</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43629,7 +43629,7 @@
         <v>45446</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>45403</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43775,7 +43775,7 @@
         <v>46164</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44998</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44650</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45323</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45039</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>45666</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44495</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46079</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46147</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46097</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>45209</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44956</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45714</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45212</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46315</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>46315</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44724</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45142</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>46205</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44771</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44790</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>45275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44637</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44715</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44865</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44785</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>44986</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45838</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>46068</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45211</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44798</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45068</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45166</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44907</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44624</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44697</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44746</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44503</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44518</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45105</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46181</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45954</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45140</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45643</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45540</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45182</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>46209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45156</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45624</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46056</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>46294</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>46071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44881</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>46079</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45377</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44624</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>46149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45740</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>46315</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45740</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45348</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45007</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45191</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44572</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44774</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44854</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45343</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45222</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44501</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>44536</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44614</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44535</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>44722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44869</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44752</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44720</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>44873</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44769</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44745</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>44579</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44807</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44739</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44770</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44640</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44725</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44778</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>44886</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44854</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44697</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>44636</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44752</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44752</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44566</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44862</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44610</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44643</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44705</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44818</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45720</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45230</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45311</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45358</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>44741</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45140</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45228</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44862</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45072</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45213</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45510</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44914</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46168</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>46168</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>46168</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44785</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45926</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44648</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44979</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45222</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45618</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46170</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44739</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45932</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44769</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45250</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45250</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>46176</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44872</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45398</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44796</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45257</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45946</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45119</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46181</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>46181</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>46183</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46170</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45244</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44701</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45270</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45518</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46188</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46188</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46188</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45365</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45299</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45299</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45022</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45110</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45149</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45555</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45331</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46196</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44580</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44517</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45217</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45066</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45322</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44907</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45230</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45230</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45993</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45256</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45994</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45993</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45995</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45566</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45244</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45386</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45777</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46229</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45350</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45008</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44852</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44883</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45414</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45790</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45790</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45790</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>46244</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>46036</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45555</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>46091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46283</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45798</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45797</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45798</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46044</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46286</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45798</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45702</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46056</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45684</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46250</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46071</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46071</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46251</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46077</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46079</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46079</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46079</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46082</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46080</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46251</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>46080</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46080</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46253</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46083</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45830</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45830</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>46295</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44887</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46296</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45702</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45478</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45729</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>46108</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>46258</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44899</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45632</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45176</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>46252</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>46125</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>46126</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44522</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>46126</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46129</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>46132</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46265</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46121</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45880</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46249</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46121</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>46121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>46132</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45540</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44636</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44859</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45280</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>46307</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46267</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46267</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46267</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45895</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44807</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>44896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44616</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45239</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45014</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45869</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44588</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>44838</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45888</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44958</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45974</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45718</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45226</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>46273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46273</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45244</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45166</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44979</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45791</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>46318</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>44524</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44897</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45209</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44986</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44988</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>44778</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45089</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45448</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45553</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45581</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44761</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45224</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45636</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>44970</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44722</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44722</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45012</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45713</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45597</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45632</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45225</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45225</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45713</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45228</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>44522</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45048</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45671</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45007</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45345</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>45082</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>44909</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45041</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44979</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45068</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>44848</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45225</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44864</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45555</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>45740</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45271</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45103</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>45022</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45081</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45081</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>45001</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45147</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44553</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>44909</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45250</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45161</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>44991</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44614</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45180</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>45528</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>44495</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45327</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>44602</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45114</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45328</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45555</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45166</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44531</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>44634</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45189</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45209</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44614</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44676</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45454</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>45740</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>44846</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>44819</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45169</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41756,7 +41756,7 @@
         <v>44733</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44907</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>45315</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44887</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45378</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45250</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45321</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>44900</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45309</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44958</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>44868</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44624</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>44624</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45411</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44970</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>44896</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45531</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44859</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45501</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>44566</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44960</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44855</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44855</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44588</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44685</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>44964</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45686</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>44742</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45446</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45403</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>46164</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>

--- a/Översikt FLEN.xlsx
+++ b/Översikt FLEN.xlsx
@@ -601,7 +601,7 @@
         <v>45477</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
         <v>45328</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -859,7 +859,7 @@
         <v>44883</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -979,7 +979,7 @@
         <v>45513</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
         <v>46175</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>45713</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1354,7 +1354,7 @@
         <v>45424</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1475,7 +1475,7 @@
         <v>45156</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44571</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1715,7 +1715,7 @@
         <v>44791</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
         <v>44998</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1948,7 +1948,7 @@
         <v>44650</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
         <v>45323</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
         <v>44624</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45039</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>45666</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>44495</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2640,7 +2640,7 @@
         <v>44078</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2755,7 +2755,7 @@
         <v>45002</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2870,7 +2870,7 @@
         <v>46037</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
         <v>46079</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3095,7 +3095,7 @@
         <v>46108</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>46147</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
         <v>46097</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3433,7 +3433,7 @@
         <v>44814</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>45209</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>44533</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3769,7 +3769,7 @@
         <v>45839</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3882,7 +3882,7 @@
         <v>45600</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3996,7 +3996,7 @@
         <v>45518</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>44956</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45714</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4332,7 +4332,7 @@
         <v>44596</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4440,7 +4440,7 @@
         <v>45212</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>44986</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4661,7 +4661,7 @@
         <v>46079</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4774,7 +4774,7 @@
         <v>45777</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4887,7 +4887,7 @@
         <v>46044</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46112</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5108,7 +5108,7 @@
         <v>46315</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5216,7 +5216,7 @@
         <v>46315</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>45518</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5432,7 +5432,7 @@
         <v>44724</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5539,7 +5539,7 @@
         <v>45142</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5655,7 +5655,7 @@
         <v>46205</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5762,7 +5762,7 @@
         <v>46071</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5869,7 +5869,7 @@
         <v>46071</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5980,7 +5980,7 @@
         <v>46071</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6087,7 +6087,7 @@
         <v>45789</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6194,7 +6194,7 @@
         <v>45965</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>45272</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45666</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6520,7 +6520,7 @@
         <v>44578</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6636,7 +6636,7 @@
         <v>44771</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6743,7 +6743,7 @@
         <v>44790</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6859,7 +6859,7 @@
         <v>45275</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44830</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7082,7 +7082,7 @@
         <v>45530</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7189,7 +7189,7 @@
         <v>44637</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44624</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7405,7 +7405,7 @@
         <v>44715</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7516,7 +7516,7 @@
         <v>44865</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7631,7 +7631,7 @@
         <v>45400</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>44785</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7843,7 +7843,7 @@
         <v>44986</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>45838</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>45798</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8166,7 +8166,7 @@
         <v>46044</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8277,7 +8277,7 @@
         <v>46155</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>46068</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>46258</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8600,7 +8600,7 @@
         <v>45211</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8706,7 +8706,7 @@
         <v>45219</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8816,7 +8816,7 @@
         <v>44826</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8922,7 +8922,7 @@
         <v>44798</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>44848</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9139,7 +9139,7 @@
         <v>44971</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>45068</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9351,7 +9351,7 @@
         <v>45166</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9462,7 +9462,7 @@
         <v>44907</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9568,7 +9568,7 @@
         <v>44624</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9674,7 +9674,7 @@
         <v>44596</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9780,7 +9780,7 @@
         <v>44697</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44746</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9995,7 +9995,7 @@
         <v>44503</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44608</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44838</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10315,7 +10315,7 @@
         <v>44735</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10420,7 +10420,7 @@
         <v>45586</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>46168</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10635,7 +10635,7 @@
         <v>44518</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10740,7 +10740,7 @@
         <v>45105</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10850,7 +10850,7 @@
         <v>45931</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45141</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44911</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11175,7 +11175,7 @@
         <v>46181</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>46181</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11394,7 +11394,7 @@
         <v>45954</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45140</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>45643</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11714,7 +11714,7 @@
         <v>45211</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11819,7 +11819,7 @@
         <v>45540</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45350</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12029,7 +12029,7 @@
         <v>45182</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>46209</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12244,7 +12244,7 @@
         <v>45156</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>45196</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>45624</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12569,7 +12569,7 @@
         <v>46035</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12679,7 +12679,7 @@
         <v>46035</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12793,7 +12793,7 @@
         <v>46056</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12898,7 +12898,7 @@
         <v>46294</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>46071</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -13113,7 +13113,7 @@
         <v>44881</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>46079</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13328,7 +13328,7 @@
         <v>45377</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13433,7 +13433,7 @@
         <v>44624</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13538,7 +13538,7 @@
         <v>46149</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13643,7 +13643,7 @@
         <v>45740</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>46315</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45510</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13963,7 +13963,7 @@
         <v>44503</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>44865</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45740</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -14288,7 +14288,7 @@
         <v>44495</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -14398,7 +14398,7 @@
         <v>45348</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -14503,7 +14503,7 @@
         <v>45007</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -14613,7 +14613,7 @@
         <v>45191</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44572</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14828,7 +14828,7 @@
         <v>44637</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>45740</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -15048,7 +15048,7 @@
         <v>45163</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -15153,7 +15153,7 @@
         <v>44785</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>44774</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -15363,7 +15363,7 @@
         <v>44854</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45343</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45222</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -15678,7 +15678,7 @@
         <v>44953</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -15783,7 +15783,7 @@
         <v>44637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44501</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>44536</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44614</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44535</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>44722</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>44869</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -16340,7 +16340,7 @@
         <v>44608</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -16418,7 +16418,7 @@
         <v>44752</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>44720</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>44873</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -16642,7 +16642,7 @@
         <v>44769</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>44745</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -16788,7 +16788,7 @@
         <v>44839</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -16861,7 +16861,7 @@
         <v>44579</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>44807</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>44855</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>44879</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>44739</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -17226,7 +17226,7 @@
         <v>44770</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>44769</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -17377,7 +17377,7 @@
         <v>44640</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -17450,7 +17450,7 @@
         <v>44725</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -17523,7 +17523,7 @@
         <v>44830</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>44643</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>44778</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44588</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -17815,7 +17815,7 @@
         <v>44839</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44769</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>44886</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -18034,7 +18034,7 @@
         <v>44854</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -18107,7 +18107,7 @@
         <v>44697</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>44578</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -18258,7 +18258,7 @@
         <v>44769</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -18331,7 +18331,7 @@
         <v>44846</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -18409,7 +18409,7 @@
         <v>44636</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -18482,7 +18482,7 @@
         <v>44752</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>44752</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -18628,7 +18628,7 @@
         <v>44566</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -18706,7 +18706,7 @@
         <v>44862</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -18779,7 +18779,7 @@
         <v>44610</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>44643</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>44636</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -19003,7 +19003,7 @@
         <v>44705</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -19076,7 +19076,7 @@
         <v>44818</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -19149,7 +19149,7 @@
         <v>45720</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>45230</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -19295,7 +19295,7 @@
         <v>45311</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -19368,7 +19368,7 @@
         <v>45358</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -19441,7 +19441,7 @@
         <v>44741</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45140</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -19587,7 +19587,7 @@
         <v>45228</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>44862</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -19738,7 +19738,7 @@
         <v>45072</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -19811,7 +19811,7 @@
         <v>45482</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>45213</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -19962,7 +19962,7 @@
         <v>45510</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -20035,7 +20035,7 @@
         <v>44914</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -20108,7 +20108,7 @@
         <v>46168</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -20181,7 +20181,7 @@
         <v>46168</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -20259,7 +20259,7 @@
         <v>46168</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>46168</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45924</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -20488,7 +20488,7 @@
         <v>44785</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -20561,7 +20561,7 @@
         <v>45926</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>46168</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -20717,7 +20717,7 @@
         <v>44648</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>46168</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -20868,7 +20868,7 @@
         <v>44979</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -20941,7 +20941,7 @@
         <v>45056</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>45222</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -21087,7 +21087,7 @@
         <v>46121</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45330</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45618</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>46170</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>44739</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -21482,7 +21482,7 @@
         <v>45932</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -21560,7 +21560,7 @@
         <v>45932</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>46175</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -21706,7 +21706,7 @@
         <v>44769</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -21779,7 +21779,7 @@
         <v>45036</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -21852,7 +21852,7 @@
         <v>45250</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45250</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -22003,7 +22003,7 @@
         <v>46176</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -22081,7 +22081,7 @@
         <v>44872</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -22154,7 +22154,7 @@
         <v>45398</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -22227,7 +22227,7 @@
         <v>45441</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -22300,7 +22300,7 @@
         <v>44796</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>45114</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -22446,7 +22446,7 @@
         <v>45257</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -22519,7 +22519,7 @@
         <v>45946</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -22592,7 +22592,7 @@
         <v>45119</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -22665,7 +22665,7 @@
         <v>44887</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -22738,7 +22738,7 @@
         <v>46181</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -22811,7 +22811,7 @@
         <v>46181</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -22884,7 +22884,7 @@
         <v>46181</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -22962,7 +22962,7 @@
         <v>46183</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -23040,7 +23040,7 @@
         <v>46170</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45244</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -23191,7 +23191,7 @@
         <v>44701</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -23264,7 +23264,7 @@
         <v>45270</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -23337,7 +23337,7 @@
         <v>45161</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45518</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>45574</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46188</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>46188</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>46188</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45964</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45365</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45299</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45299</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45022</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45110</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>45149</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -24369,7 +24369,7 @@
         <v>45555</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -24442,7 +24442,7 @@
         <v>45331</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>46196</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>45974</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>45140</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>44931</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44580</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>44517</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45217</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -25041,7 +25041,7 @@
         <v>45066</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -25114,7 +25114,7 @@
         <v>45322</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>44907</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>45667</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -25333,7 +25333,7 @@
         <v>45230</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -25406,7 +25406,7 @@
         <v>45230</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -25479,7 +25479,7 @@
         <v>45013</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -25552,7 +25552,7 @@
         <v>45993</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -25625,7 +25625,7 @@
         <v>45256</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>45994</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -25776,7 +25776,7 @@
         <v>45994</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45993</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>45993</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>45995</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -26078,7 +26078,7 @@
         <v>45995</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -26151,7 +26151,7 @@
         <v>45566</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -26224,7 +26224,7 @@
         <v>45244</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -26302,7 +26302,7 @@
         <v>45386</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>46000</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -26453,7 +26453,7 @@
         <v>45777</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>46229</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45350</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -26677,7 +26677,7 @@
         <v>45252</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -26750,7 +26750,7 @@
         <v>45008</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -26823,7 +26823,7 @@
         <v>44852</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -26896,7 +26896,7 @@
         <v>44883</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>45414</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -27042,7 +27042,7 @@
         <v>46240</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -27115,7 +27115,7 @@
         <v>45790</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -27188,7 +27188,7 @@
         <v>45790</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -27261,7 +27261,7 @@
         <v>45790</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -27334,7 +27334,7 @@
         <v>46244</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -27407,7 +27407,7 @@
         <v>46036</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -27485,7 +27485,7 @@
         <v>45555</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -27558,7 +27558,7 @@
         <v>46091</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -27631,7 +27631,7 @@
         <v>45610</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -27704,7 +27704,7 @@
         <v>46283</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45798</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -27855,7 +27855,7 @@
         <v>45797</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -27928,7 +27928,7 @@
         <v>45798</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>46044</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>46286</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45798</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -28220,7 +28220,7 @@
         <v>45798</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -28293,7 +28293,7 @@
         <v>45702</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -28366,7 +28366,7 @@
         <v>46056</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>46044</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -28517,7 +28517,7 @@
         <v>45684</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -28590,7 +28590,7 @@
         <v>46175</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -28663,7 +28663,7 @@
         <v>46250</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -28736,7 +28736,7 @@
         <v>46293</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -28814,7 +28814,7 @@
         <v>45817</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>46071</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -28965,7 +28965,7 @@
         <v>46071</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -29038,7 +29038,7 @@
         <v>46251</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>46077</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -29189,7 +29189,7 @@
         <v>46079</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -29267,7 +29267,7 @@
         <v>46251</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -29345,7 +29345,7 @@
         <v>46079</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>46079</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -29501,7 +29501,7 @@
         <v>46082</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -29574,7 +29574,7 @@
         <v>46080</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>46251</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -29730,7 +29730,7 @@
         <v>46080</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>46080</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -29886,7 +29886,7 @@
         <v>46253</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -29959,7 +29959,7 @@
         <v>46083</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -30037,7 +30037,7 @@
         <v>45830</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -30110,7 +30110,7 @@
         <v>45830</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -30183,7 +30183,7 @@
         <v>46295</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -30256,7 +30256,7 @@
         <v>46205</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -30329,7 +30329,7 @@
         <v>44887</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>46296</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -30475,7 +30475,7 @@
         <v>46258</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -30553,7 +30553,7 @@
         <v>45702</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -30626,7 +30626,7 @@
         <v>45478</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -30699,7 +30699,7 @@
         <v>45729</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -30772,7 +30772,7 @@
         <v>46108</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -30850,7 +30850,7 @@
         <v>46258</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>46112</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -31001,7 +31001,7 @@
         <v>46113</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -31074,7 +31074,7 @@
         <v>46258</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -31152,7 +31152,7 @@
         <v>44899</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -31225,7 +31225,7 @@
         <v>45632</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45176</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>46252</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -31444,7 +31444,7 @@
         <v>46125</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -31522,7 +31522,7 @@
         <v>46126</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -31595,7 +31595,7 @@
         <v>44522</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>46252</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>46126</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -31814,7 +31814,7 @@
         <v>46129</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -31887,7 +31887,7 @@
         <v>46132</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -31965,7 +31965,7 @@
         <v>46265</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>46121</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -32111,7 +32111,7 @@
         <v>45880</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -32184,7 +32184,7 @@
         <v>46249</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -32257,7 +32257,7 @@
         <v>46121</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -32330,7 +32330,7 @@
         <v>46121</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>46132</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45540</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -32554,7 +32554,7 @@
         <v>45161</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -32627,7 +32627,7 @@
         <v>44636</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -32700,7 +32700,7 @@
         <v>44859</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -32778,7 +32778,7 @@
         <v>45280</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -32851,7 +32851,7 @@
         <v>45805</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -32924,7 +32924,7 @@
         <v>46185</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -32997,7 +32997,7 @@
         <v>46307</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>46267</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -33148,7 +33148,7 @@
         <v>46266</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -33226,7 +33226,7 @@
         <v>46267</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -33304,7 +33304,7 @@
         <v>46267</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45895</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -33455,7 +33455,7 @@
         <v>44807</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -33528,7 +33528,7 @@
         <v>45239</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -33606,7 +33606,7 @@
         <v>44896</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -33684,7 +33684,7 @@
         <v>44616</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -33757,7 +33757,7 @@
         <v>45239</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -33835,7 +33835,7 @@
         <v>45014</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45869</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>44588</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -34059,7 +34059,7 @@
         <v>44838</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -34132,7 +34132,7 @@
         <v>45888</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -34205,7 +34205,7 @@
         <v>44958</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -34283,7 +34283,7 @@
         <v>45974</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45718</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -34429,7 +34429,7 @@
         <v>45226</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>46273</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -34580,7 +34580,7 @@
         <v>46273</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -34658,7 +34658,7 @@
         <v>45244</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>46273</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45166</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -34882,7 +34882,7 @@
         <v>44979</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -34955,7 +34955,7 @@
         <v>45791</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -35028,7 +35028,7 @@
         <v>46318</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -35101,7 +35101,7 @@
         <v>45993</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -35174,7 +35174,7 @@
         <v>44524</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>44897</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -35325,7 +35325,7 @@
         <v>45209</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>44986</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>44988</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -35549,7 +35549,7 @@
         <v>44778</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -35622,7 +35622,7 @@
         <v>45089</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -35695,7 +35695,7 @@
         <v>45448</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -35768,7 +35768,7 @@
         <v>45553</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -35841,7 +35841,7 @@
         <v>44911</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -35919,7 +35919,7 @@
         <v>45581</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -35992,7 +35992,7 @@
         <v>44761</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45224</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -36143,7 +36143,7 @@
         <v>45636</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -36216,7 +36216,7 @@
         <v>44970</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -36289,7 +36289,7 @@
         <v>44722</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -36362,7 +36362,7 @@
         <v>44722</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -36435,7 +36435,7 @@
         <v>45012</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -36513,7 +36513,7 @@
         <v>45713</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -36586,7 +36586,7 @@
         <v>45597</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -36659,7 +36659,7 @@
         <v>45632</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -36732,7 +36732,7 @@
         <v>45225</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -36805,7 +36805,7 @@
         <v>45225</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45030</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -36951,7 +36951,7 @@
         <v>45713</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45228</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>44522</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -37175,7 +37175,7 @@
         <v>45211</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -37248,7 +37248,7 @@
         <v>45048</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -37321,7 +37321,7 @@
         <v>45671</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -37394,7 +37394,7 @@
         <v>45007</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -37467,7 +37467,7 @@
         <v>45345</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -37540,7 +37540,7 @@
         <v>45082</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -37613,7 +37613,7 @@
         <v>44909</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>45041</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -37764,7 +37764,7 @@
         <v>44979</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45068</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -37915,7 +37915,7 @@
         <v>44848</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -37993,7 +37993,7 @@
         <v>45225</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>44864</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -38139,7 +38139,7 @@
         <v>45216</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -38217,7 +38217,7 @@
         <v>45555</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -38290,7 +38290,7 @@
         <v>45740</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -38368,7 +38368,7 @@
         <v>45260</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -38441,7 +38441,7 @@
         <v>45271</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -38514,7 +38514,7 @@
         <v>45103</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -38587,7 +38587,7 @@
         <v>45022</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -38660,7 +38660,7 @@
         <v>45034</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -38733,7 +38733,7 @@
         <v>45104</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>45081</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45081</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -38952,7 +38952,7 @@
         <v>45001</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45147</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -39103,7 +39103,7 @@
         <v>44553</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -39176,7 +39176,7 @@
         <v>44909</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -39254,7 +39254,7 @@
         <v>45250</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45161</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -39405,7 +39405,7 @@
         <v>45163</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -39478,7 +39478,7 @@
         <v>44980</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -39551,7 +39551,7 @@
         <v>44991</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44957</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -39697,7 +39697,7 @@
         <v>44614</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -39770,7 +39770,7 @@
         <v>45180</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -39843,7 +39843,7 @@
         <v>45528</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -39916,7 +39916,7 @@
         <v>44544</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -39989,7 +39989,7 @@
         <v>45175</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -40062,7 +40062,7 @@
         <v>45163</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>44495</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45327</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45161</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>44610</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -40427,7 +40427,7 @@
         <v>44602</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -40500,7 +40500,7 @@
         <v>45114</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -40573,7 +40573,7 @@
         <v>45328</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>45555</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -40719,7 +40719,7 @@
         <v>45166</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -40792,7 +40792,7 @@
         <v>44531</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -40865,7 +40865,7 @@
         <v>44634</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -40938,7 +40938,7 @@
         <v>45189</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -41016,7 +41016,7 @@
         <v>45209</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -41089,7 +41089,7 @@
         <v>44614</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -41162,7 +41162,7 @@
         <v>44676</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45454</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>45740</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -41386,7 +41386,7 @@
         <v>45230</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -41459,7 +41459,7 @@
         <v>44846</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -41537,7 +41537,7 @@
         <v>44819</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45057</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45169</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -41756,7 +41756,7 @@
         <v>44733</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -41829,7 +41829,7 @@
         <v>44907</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -41902,7 +41902,7 @@
         <v>45315</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44887</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45378</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -42126,7 +42126,7 @@
         <v>45163</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -42199,7 +42199,7 @@
         <v>45250</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -42272,7 +42272,7 @@
         <v>45321</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -42345,7 +42345,7 @@
         <v>44900</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -42418,7 +42418,7 @@
         <v>45309</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>44958</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>44868</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -42642,7 +42642,7 @@
         <v>44624</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -42715,7 +42715,7 @@
         <v>44624</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -42788,7 +42788,7 @@
         <v>45411</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -42861,7 +42861,7 @@
         <v>44970</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>44896</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -43017,7 +43017,7 @@
         <v>45244</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -43095,7 +43095,7 @@
         <v>45531</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -43168,7 +43168,7 @@
         <v>44859</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -43246,7 +43246,7 @@
         <v>45501</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -43319,7 +43319,7 @@
         <v>44566</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -43392,7 +43392,7 @@
         <v>44960</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -43465,7 +43465,7 @@
         <v>44855</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44855</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -43611,7 +43611,7 @@
         <v>44588</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -43684,7 +43684,7 @@
         <v>44685</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>44964</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -43840,7 +43840,7 @@
         <v>45686</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -43913,7 +43913,7 @@
         <v>44742</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -43986,7 +43986,7 @@
         <v>45446</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -44059,7 +44059,7 @@
         <v>45403</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -44132,7 +44132,7 @@
         <v>46164</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
